--- a/modello.xlsx
+++ b/modello.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maurizio\Desktop\progetto_modulo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{610581F4-E171-4630-A9E9-FBD3DD1E87D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D984CB9A-173E-4EF5-A687-ECA6A8A6F764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="6" state="hidden" r:id="rId1"/>
     <sheet name="Modulo" sheetId="7" r:id="rId2"/>
+    <sheet name="Pagina 2 ( allegato)" sheetId="8" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Modulo!$B$1:$D$85</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Modulo!$B$1:$D$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Pagina 2 ( allegato)'!$B$1:$D$38</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
   <si>
     <t>TIPOLOGIA  PRODOTTO</t>
   </si>
@@ -169,18 +171,6 @@
     <t xml:space="preserve">allegato 1          </t>
   </si>
   <si>
-    <t>Caratteristica di lampeggio</t>
-  </si>
-  <si>
-    <t>Portata                          MN</t>
-  </si>
-  <si>
-    <t>Colore della luce</t>
-  </si>
-  <si>
-    <t>Sincronismo GPS</t>
-  </si>
-  <si>
     <t>Segue allegato</t>
   </si>
 </sst>
@@ -191,7 +181,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mmmm/yyyy"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -312,6 +302,11 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial MT"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -830,60 +825,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -903,6 +844,60 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -967,25 +962,30 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:colOff>89793</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>50896</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>362352</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>14066</xdr:rowOff>
+      <xdr:colOff>444525</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>145</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Immagine 4">
+        <xdr:cNvPr id="2" name="Immagine 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5E139B6-BE22-4CE6-A33C-AB8415E44B9E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38E6B9C9-CBEE-4F94-9407-846F3CBA5A42}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1001,8 +1001,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="617220" y="10904220"/>
-          <a:ext cx="2404512" cy="745586"/>
+          <a:off x="620575" y="101793"/>
+          <a:ext cx="2056145" cy="719974"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1438,7 +1438,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A07E4BB-79A5-4D84-AAD0-26E3BA66DC3E}">
   <sheetPr codeName="Foglio3"/>
-  <dimension ref="A1:Y114"/>
+  <dimension ref="A1:Y66"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="3"/>
@@ -1446,7 +1446,7 @@
     <col min="3" max="3" width="12.6640625" customWidth="1"/>
     <col min="4" max="4" width="53.1640625" style="28" customWidth="1"/>
     <col min="5" max="5" width="23.5" style="47" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="0" style="4" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" style="4" customWidth="1"/>
     <col min="7" max="25" width="8.83203125" style="4"/>
   </cols>
   <sheetData>
@@ -1507,18 +1507,18 @@
       <c r="E3" s="52"/>
     </row>
     <row r="4" spans="1:25" ht="27" customHeight="1">
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="67"/>
+      <c r="C4" s="72"/>
       <c r="D4" s="36"/>
       <c r="E4" s="46"/>
     </row>
     <row r="5" spans="1:25" ht="27" customHeight="1" thickBot="1">
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="73" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="69"/>
+      <c r="C5" s="74"/>
       <c r="D5" s="35"/>
       <c r="E5" s="46"/>
     </row>
@@ -1528,12 +1528,12 @@
       <c r="D6" s="12"/>
     </row>
     <row r="7" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="54"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="63"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="68"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -1556,10 +1556,10 @@
       <c r="Y7" s="4"/>
     </row>
     <row r="8" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B8" s="55"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="63"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="68"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -1582,17 +1582,17 @@
       <c r="Y8" s="4"/>
     </row>
     <row r="9" spans="1:25" ht="21" customHeight="1">
-      <c r="B9" s="55"/>
-      <c r="C9" s="56"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="63"/>
+      <c r="B9" s="60"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="68"/>
     </row>
     <row r="10" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
       <c r="A10" s="31"/>
-      <c r="B10" s="64" t="s">
+      <c r="B10" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="65"/>
+      <c r="C10" s="70"/>
       <c r="D10" s="43"/>
       <c r="E10" s="48" t="str">
         <f>MID(D10,1,6)</f>
@@ -1621,11 +1621,11 @@
     </row>
     <row r="11" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A11" s="31"/>
-      <c r="B11" s="59" t="str">
+      <c r="B11" s="64" t="str">
         <f>IF(D10=""," ","Q.ta")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C11" s="60"/>
+      <c r="C11" s="65"/>
       <c r="D11" s="40"/>
       <c r="E11" s="48"/>
       <c r="F11" s="32"/>
@@ -1651,11 +1651,11 @@
     </row>
     <row r="12" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A12" s="31"/>
-      <c r="B12" s="59" t="str">
+      <c r="B12" s="64" t="str">
         <f>IF(E10="INTERN","Caratteristica di lampeggio",IF(E10="FANALI","Caratteristica di lampeggio",""))</f>
         <v/>
       </c>
-      <c r="C12" s="60"/>
+      <c r="C12" s="65"/>
       <c r="D12" s="41"/>
       <c r="E12" s="48"/>
       <c r="F12" s="32"/>
@@ -1681,11 +1681,11 @@
     </row>
     <row r="13" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A13" s="31"/>
-      <c r="B13" s="59" t="str">
+      <c r="B13" s="64" t="str">
         <f>IF(E10="INTERN","Portata                          MN",IF(E10="FANALI","Portata                          MN",""))</f>
         <v/>
       </c>
-      <c r="C13" s="60"/>
+      <c r="C13" s="65"/>
       <c r="D13" s="42"/>
       <c r="E13" s="48"/>
       <c r="F13" s="32"/>
@@ -1711,11 +1711,11 @@
     </row>
     <row r="14" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A14" s="31"/>
-      <c r="B14" s="59" t="str">
+      <c r="B14" s="64" t="str">
         <f>IF(E10="INTERN","Colore della luce",IF(E10="FANALI","Colore della luce",""))</f>
         <v/>
       </c>
-      <c r="C14" s="60"/>
+      <c r="C14" s="65"/>
       <c r="D14" s="42"/>
       <c r="E14" s="48" t="s">
         <v>41</v>
@@ -1743,11 +1743,11 @@
     </row>
     <row r="15" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A15" s="31"/>
-      <c r="B15" s="59" t="str">
+      <c r="B15" s="64" t="str">
         <f>IF(E10="INTERN","Sincronismo GPS",IF(E10="FANALI","Sincronismo GPS",""))</f>
         <v/>
       </c>
-      <c r="C15" s="60"/>
+      <c r="C15" s="65"/>
       <c r="D15" s="42"/>
       <c r="E15" s="48"/>
       <c r="F15" s="32"/>
@@ -1773,11 +1773,11 @@
     </row>
     <row r="16" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A16" s="31"/>
-      <c r="B16" s="61" t="str">
-        <f>IF(D10=""," ","Note/specifiche")</f>
+      <c r="B16" s="66" t="str">
+        <f>IF(D10=""," ","NOTE / SPECIFICHE TECNICHE")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C16" s="62"/>
+      <c r="C16" s="67"/>
       <c r="D16" s="44"/>
       <c r="E16" s="48"/>
       <c r="F16" s="32"/>
@@ -1819,12 +1819,12 @@
       <c r="D19" s="26"/>
     </row>
     <row r="20" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B20" s="53" t="s">
+      <c r="B20" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="54"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="63"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="68"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
@@ -1847,10 +1847,10 @@
       <c r="Y20" s="4"/>
     </row>
     <row r="21" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B21" s="55"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="63"/>
+      <c r="B21" s="60"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="68"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
@@ -1873,17 +1873,17 @@
       <c r="Y21" s="4"/>
     </row>
     <row r="22" spans="1:25" ht="21" customHeight="1">
-      <c r="B22" s="55"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="63"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="68"/>
     </row>
     <row r="23" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
       <c r="A23" s="31"/>
-      <c r="B23" s="64" t="s">
+      <c r="B23" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="C23" s="65"/>
+      <c r="C23" s="70"/>
       <c r="D23" s="43"/>
       <c r="E23" s="48" t="str">
         <f>MID(D23,1,6)</f>
@@ -1912,11 +1912,11 @@
     </row>
     <row r="24" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A24" s="31"/>
-      <c r="B24" s="59" t="str">
+      <c r="B24" s="64" t="str">
         <f>IF(D23=""," ","Q.ta")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C24" s="60"/>
+      <c r="C24" s="65"/>
       <c r="D24" s="40"/>
       <c r="E24" s="48"/>
       <c r="F24" s="32"/>
@@ -1942,11 +1942,11 @@
     </row>
     <row r="25" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A25" s="31"/>
-      <c r="B25" s="59" t="str">
+      <c r="B25" s="64" t="str">
         <f>IF(E23="INTERN","Caratteristica di lampeggio",IF(E23="FANALI","Caratteristica di lampeggio",""))</f>
         <v/>
       </c>
-      <c r="C25" s="60"/>
+      <c r="C25" s="65"/>
       <c r="D25" s="41"/>
       <c r="E25" s="48"/>
       <c r="F25" s="32"/>
@@ -1972,11 +1972,11 @@
     </row>
     <row r="26" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A26" s="31"/>
-      <c r="B26" s="59" t="str">
+      <c r="B26" s="64" t="str">
         <f>IF(E23="INTERN","Portata                          MN",IF(E23="FANALI","Portata                          MN",""))</f>
         <v/>
       </c>
-      <c r="C26" s="60"/>
+      <c r="C26" s="65"/>
       <c r="D26" s="42"/>
       <c r="E26" s="48"/>
       <c r="F26" s="32"/>
@@ -2002,11 +2002,11 @@
     </row>
     <row r="27" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A27" s="31"/>
-      <c r="B27" s="59" t="str">
+      <c r="B27" s="64" t="str">
         <f>IF(E23="INTERN","Colore della luce",IF(E23="FANALI","Colore della luce",""))</f>
         <v/>
       </c>
-      <c r="C27" s="60"/>
+      <c r="C27" s="65"/>
       <c r="D27" s="42"/>
       <c r="E27" s="48"/>
       <c r="F27" s="32"/>
@@ -2032,11 +2032,11 @@
     </row>
     <row r="28" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A28" s="31"/>
-      <c r="B28" s="59" t="str">
+      <c r="B28" s="64" t="str">
         <f>IF(E23="INTERN","Sincronismo GPS",IF(E23="FANALI","Sincronismo GPS",""))</f>
         <v/>
       </c>
-      <c r="C28" s="60"/>
+      <c r="C28" s="65"/>
       <c r="D28" s="42"/>
       <c r="E28" s="48"/>
       <c r="F28" s="32"/>
@@ -2062,11 +2062,11 @@
     </row>
     <row r="29" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A29" s="31"/>
-      <c r="B29" s="61" t="str">
-        <f>IF(D23=""," ","Note/specifiche")</f>
+      <c r="B29" s="66" t="str">
+        <f>IF(D23=""," ","NOTE / SPECIFICHE TECNICHE")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C29" s="62"/>
+      <c r="C29" s="67"/>
       <c r="D29" s="44"/>
       <c r="E29" s="48"/>
       <c r="F29" s="32"/>
@@ -2096,12 +2096,12 @@
       <c r="D30" s="25"/>
     </row>
     <row r="31" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B31" s="53" t="s">
+      <c r="B31" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="54"/>
-      <c r="D31" s="71"/>
-      <c r="E31" s="63"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="68"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -2124,10 +2124,10 @@
       <c r="Y31" s="4"/>
     </row>
     <row r="32" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B32" s="55"/>
-      <c r="C32" s="56"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="63"/>
+      <c r="B32" s="60"/>
+      <c r="C32" s="61"/>
+      <c r="D32" s="54"/>
+      <c r="E32" s="68"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
@@ -2150,17 +2150,17 @@
       <c r="Y32" s="4"/>
     </row>
     <row r="33" spans="1:25" ht="21" customHeight="1">
-      <c r="B33" s="55"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="72"/>
-      <c r="E33" s="63"/>
+      <c r="B33" s="60"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="68"/>
     </row>
     <row r="34" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
       <c r="A34" s="31"/>
-      <c r="B34" s="64" t="s">
+      <c r="B34" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="C34" s="65"/>
+      <c r="C34" s="70"/>
       <c r="D34" s="43"/>
       <c r="E34" s="48" t="str">
         <f>MID(D34,1,6)</f>
@@ -2189,11 +2189,11 @@
     </row>
     <row r="35" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A35" s="31"/>
-      <c r="B35" s="59" t="str">
+      <c r="B35" s="64" t="str">
         <f>IF(D34=""," ","Q.ta")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C35" s="60"/>
+      <c r="C35" s="65"/>
       <c r="D35" s="40"/>
       <c r="E35" s="48"/>
       <c r="F35" s="32"/>
@@ -2219,10 +2219,11 @@
     </row>
     <row r="36" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A36" s="31"/>
-      <c r="B36" s="59" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" s="60"/>
+      <c r="B36" s="64" t="str">
+        <f>IF(E34="INTERN","Caratteristica di lampeggio",IF(E34="FANALI","Caratteristica di lampeggio",""))</f>
+        <v/>
+      </c>
+      <c r="C36" s="65"/>
       <c r="D36" s="41"/>
       <c r="E36" s="48"/>
       <c r="F36" s="32"/>
@@ -2248,10 +2249,11 @@
     </row>
     <row r="37" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A37" s="31"/>
-      <c r="B37" s="59" t="s">
-        <v>45</v>
-      </c>
-      <c r="C37" s="60"/>
+      <c r="B37" s="64" t="str">
+        <f>IF(E34="INTERN","Portata                          MN",IF(E34="FANALI","Portata                          MN",""))</f>
+        <v/>
+      </c>
+      <c r="C37" s="65"/>
       <c r="D37" s="42"/>
       <c r="E37" s="48"/>
       <c r="F37" s="32"/>
@@ -2277,10 +2279,11 @@
     </row>
     <row r="38" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A38" s="31"/>
-      <c r="B38" s="59" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="60"/>
+      <c r="B38" s="64" t="str">
+        <f>IF(E34="INTERN","Colore della luce",IF(E34="FANALI","Colore della luce",""))</f>
+        <v/>
+      </c>
+      <c r="C38" s="65"/>
       <c r="D38" s="42"/>
       <c r="E38" s="48"/>
       <c r="F38" s="32"/>
@@ -2306,10 +2309,11 @@
     </row>
     <row r="39" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A39" s="31"/>
-      <c r="B39" s="59" t="s">
-        <v>47</v>
-      </c>
-      <c r="C39" s="60"/>
+      <c r="B39" s="64" t="str">
+        <f>IF(E34="INTERN","Sincronismo GPS",IF(E34="FANALI","Sincronismo GPS",""))</f>
+        <v/>
+      </c>
+      <c r="C39" s="65"/>
       <c r="D39" s="42"/>
       <c r="E39" s="48"/>
       <c r="F39" s="32"/>
@@ -2335,11 +2339,11 @@
     </row>
     <row r="40" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A40" s="31"/>
-      <c r="B40" s="61" t="str">
-        <f>IF(D34=""," ","Note/specifiche")</f>
+      <c r="B40" s="66" t="str">
+        <f>IF(D34=""," ","NOTE / SPECIFICHE TECNICHE")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C40" s="62"/>
+      <c r="C40" s="67"/>
       <c r="D40" s="44"/>
       <c r="E40" s="48"/>
       <c r="F40" s="32"/>
@@ -2370,10 +2374,10 @@
       <c r="E41" s="46"/>
     </row>
     <row r="42" spans="1:25" ht="15" thickBot="1">
-      <c r="B42" s="57" t="s">
+      <c r="B42" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="58"/>
+      <c r="C42" s="63"/>
       <c r="D42" s="16"/>
       <c r="E42" s="46"/>
     </row>
@@ -2383,10 +2387,10 @@
       <c r="E43" s="46"/>
     </row>
     <row r="44" spans="1:25" ht="13.5" thickBot="1">
-      <c r="B44" s="57" t="s">
+      <c r="B44" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="C44" s="58"/>
+      <c r="C44" s="63"/>
       <c r="D44" s="17"/>
       <c r="E44" s="46"/>
     </row>
@@ -2403,11 +2407,11 @@
       </c>
       <c r="C46" s="20"/>
       <c r="D46" s="50" t="str">
-        <f>IF(F55=1,E46,"")</f>
+        <f>IFERROR(IF('Pagina 2 ( allegato)'!F8=1,E46,""),"")</f>
         <v/>
       </c>
       <c r="E46" s="46" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:25" s="9" customFormat="1" ht="4.1500000000000004" customHeight="1">
@@ -2437,14 +2441,11 @@
       <c r="X47" s="4"/>
       <c r="Y47" s="4"/>
     </row>
-    <row r="48" spans="1:25" s="9" customFormat="1" ht="61.15" customHeight="1">
-      <c r="A48" s="3"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="45" t="s">
-        <v>43</v>
-      </c>
-      <c r="E48" s="47"/>
+    <row r="48" spans="1:25" s="3" customFormat="1">
+      <c r="B48" s="34"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="46"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
@@ -2466,39 +2467,81 @@
       <c r="X48" s="4"/>
       <c r="Y48" s="4"/>
     </row>
-    <row r="49" spans="1:25" ht="16.5">
-      <c r="B49" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C49" s="39">
-        <f>D5</f>
-        <v>0</v>
-      </c>
-      <c r="D49" s="30"/>
+    <row r="49" spans="4:25" s="3" customFormat="1">
+      <c r="D49" s="23"/>
       <c r="E49" s="46"/>
-    </row>
-    <row r="50" spans="1:25" ht="27" customHeight="1">
-      <c r="B50" s="70">
-        <f>D4</f>
-        <v>0</v>
-      </c>
-      <c r="C50" s="70"/>
-      <c r="D50" s="33"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4"/>
+      <c r="S49" s="4"/>
+      <c r="T49" s="4"/>
+      <c r="U49" s="4"/>
+      <c r="V49" s="4"/>
+      <c r="W49" s="4"/>
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4"/>
+    </row>
+    <row r="50" spans="4:25" s="3" customFormat="1">
+      <c r="D50" s="23"/>
       <c r="E50" s="46"/>
-    </row>
-    <row r="51" spans="1:25" ht="27" customHeight="1" thickBot="1">
-      <c r="B51" s="37"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="38"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="4"/>
+      <c r="S50" s="4"/>
+      <c r="T50" s="4"/>
+      <c r="U50" s="4"/>
+      <c r="V50" s="4"/>
+      <c r="W50" s="4"/>
+      <c r="X50" s="4"/>
+      <c r="Y50" s="4"/>
+    </row>
+    <row r="51" spans="4:25" s="3" customFormat="1">
+      <c r="D51" s="23"/>
       <c r="E51" s="46"/>
-    </row>
-    <row r="52" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B52" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="C52" s="54"/>
-      <c r="D52" s="71"/>
-      <c r="E52" s="63"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4"/>
+      <c r="R51" s="4"/>
+      <c r="S51" s="4"/>
+      <c r="T51" s="4"/>
+      <c r="U51" s="4"/>
+      <c r="V51" s="4"/>
+      <c r="W51" s="4"/>
+      <c r="X51" s="4"/>
+      <c r="Y51" s="4"/>
+    </row>
+    <row r="52" spans="4:25" s="3" customFormat="1">
+      <c r="D52" s="23"/>
+      <c r="E52" s="46"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
@@ -2520,11 +2563,9 @@
       <c r="X52" s="4"/>
       <c r="Y52" s="4"/>
     </row>
-    <row r="53" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B53" s="55"/>
-      <c r="C53" s="56"/>
-      <c r="D53" s="72"/>
-      <c r="E53" s="63"/>
+    <row r="53" spans="4:25" s="3" customFormat="1">
+      <c r="D53" s="23"/>
+      <c r="E53" s="46"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
       <c r="H53" s="4"/>
@@ -2546,1448 +2587,258 @@
       <c r="X53" s="4"/>
       <c r="Y53" s="4"/>
     </row>
-    <row r="54" spans="1:25" ht="21" customHeight="1">
-      <c r="B54" s="55"/>
-      <c r="C54" s="56"/>
-      <c r="D54" s="72"/>
-      <c r="E54" s="63"/>
-    </row>
-    <row r="55" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
-      <c r="A55" s="31"/>
-      <c r="B55" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="C55" s="65"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="48" t="str">
-        <f>MID(D55,1,6)</f>
-        <v/>
-      </c>
-      <c r="F55" s="48">
-        <f>IF(D55="",0,1)</f>
-        <v>0</v>
-      </c>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="32"/>
-      <c r="J55" s="32"/>
-      <c r="K55" s="32"/>
-      <c r="L55" s="32"/>
-      <c r="M55" s="32"/>
-      <c r="N55" s="32"/>
-      <c r="O55" s="32"/>
-      <c r="P55" s="32"/>
-      <c r="Q55" s="32"/>
-      <c r="R55" s="32"/>
-      <c r="S55" s="32"/>
-      <c r="T55" s="32"/>
-      <c r="U55" s="32"/>
-      <c r="V55" s="32"/>
-      <c r="W55" s="32"/>
-      <c r="X55" s="32"/>
-      <c r="Y55" s="32"/>
-    </row>
-    <row r="56" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A56" s="31"/>
-      <c r="B56" s="59" t="str">
-        <f>IF(D55=""," ","Q.ta")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="C56" s="60"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="32"/>
-      <c r="I56" s="32"/>
-      <c r="J56" s="32"/>
-      <c r="K56" s="32"/>
-      <c r="L56" s="32"/>
-      <c r="M56" s="32"/>
-      <c r="N56" s="32"/>
-      <c r="O56" s="32"/>
-      <c r="P56" s="32"/>
-      <c r="Q56" s="32"/>
-      <c r="R56" s="32"/>
-      <c r="S56" s="32"/>
-      <c r="T56" s="32"/>
-      <c r="U56" s="32"/>
-      <c r="V56" s="32"/>
-      <c r="W56" s="32"/>
-      <c r="X56" s="32"/>
-      <c r="Y56" s="32"/>
-    </row>
-    <row r="57" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A57" s="31"/>
-      <c r="B57" s="59" t="str">
-        <f>IF(E55="INTERN","Caratteristica di lampeggio",IF(E55="FANALI","Caratteristica di lampeggio",""))</f>
-        <v/>
-      </c>
-      <c r="C57" s="60"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="48"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="32"/>
-      <c r="I57" s="32"/>
-      <c r="J57" s="32"/>
-      <c r="K57" s="32"/>
-      <c r="L57" s="32"/>
-      <c r="M57" s="32"/>
-      <c r="N57" s="32"/>
-      <c r="O57" s="32"/>
-      <c r="P57" s="32"/>
-      <c r="Q57" s="32"/>
-      <c r="R57" s="32"/>
-      <c r="S57" s="32"/>
-      <c r="T57" s="32"/>
-      <c r="U57" s="32"/>
-      <c r="V57" s="32"/>
-      <c r="W57" s="32"/>
-      <c r="X57" s="32"/>
-      <c r="Y57" s="32"/>
-    </row>
-    <row r="58" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A58" s="31"/>
-      <c r="B58" s="59" t="str">
-        <f>IF(E55="INTERN","Portata                          MN",IF(E55="FANALI","Portata                          MN",""))</f>
-        <v/>
-      </c>
-      <c r="C58" s="60"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="32"/>
-      <c r="I58" s="32"/>
-      <c r="J58" s="32"/>
-      <c r="K58" s="32"/>
-      <c r="L58" s="32"/>
-      <c r="M58" s="32"/>
-      <c r="N58" s="32"/>
-      <c r="O58" s="32"/>
-      <c r="P58" s="32"/>
-      <c r="Q58" s="32"/>
-      <c r="R58" s="32"/>
-      <c r="S58" s="32"/>
-      <c r="T58" s="32"/>
-      <c r="U58" s="32"/>
-      <c r="V58" s="32"/>
-      <c r="W58" s="32"/>
-      <c r="X58" s="32"/>
-      <c r="Y58" s="32"/>
-    </row>
-    <row r="59" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A59" s="31"/>
-      <c r="B59" s="59" t="str">
-        <f>IF(E55="INTERN","Colore della luce",IF(E55="FANALI","Colore della luce",""))</f>
-        <v/>
-      </c>
-      <c r="C59" s="60"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="32"/>
-      <c r="I59" s="32"/>
-      <c r="J59" s="32"/>
-      <c r="K59" s="32"/>
-      <c r="L59" s="32"/>
-      <c r="M59" s="32"/>
-      <c r="N59" s="32"/>
-      <c r="O59" s="32"/>
-      <c r="P59" s="32"/>
-      <c r="Q59" s="32"/>
-      <c r="R59" s="32"/>
-      <c r="S59" s="32"/>
-      <c r="T59" s="32"/>
-      <c r="U59" s="32"/>
-      <c r="V59" s="32"/>
-      <c r="W59" s="32"/>
-      <c r="X59" s="32"/>
-      <c r="Y59" s="32"/>
-    </row>
-    <row r="60" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A60" s="31"/>
-      <c r="B60" s="59" t="str">
-        <f>IF(E55="INTERN","Sincronismo GPS",IF(E55="FANALI","Sincronismo GPS",""))</f>
-        <v/>
-      </c>
-      <c r="C60" s="60"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="48"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="32"/>
-      <c r="I60" s="32"/>
-      <c r="J60" s="32"/>
-      <c r="K60" s="32"/>
-      <c r="L60" s="32"/>
-      <c r="M60" s="32"/>
-      <c r="N60" s="32"/>
-      <c r="O60" s="32"/>
-      <c r="P60" s="32"/>
-      <c r="Q60" s="32"/>
-      <c r="R60" s="32"/>
-      <c r="S60" s="32"/>
-      <c r="T60" s="32"/>
-      <c r="U60" s="32"/>
-      <c r="V60" s="32"/>
-      <c r="W60" s="32"/>
-      <c r="X60" s="32"/>
-      <c r="Y60" s="32"/>
-    </row>
-    <row r="61" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="A61" s="31"/>
-      <c r="B61" s="61" t="str">
-        <f>IF(D55=""," ","Note/specifiche")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="C61" s="62"/>
-      <c r="D61" s="51"/>
-      <c r="E61" s="48"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="32"/>
-      <c r="H61" s="32"/>
-      <c r="I61" s="32"/>
-      <c r="J61" s="32"/>
-      <c r="K61" s="32"/>
-      <c r="L61" s="32"/>
-      <c r="M61" s="32"/>
-      <c r="N61" s="32"/>
-      <c r="O61" s="32"/>
-      <c r="P61" s="32"/>
-      <c r="Q61" s="32"/>
-      <c r="R61" s="32"/>
-      <c r="S61" s="32"/>
-      <c r="T61" s="32"/>
-      <c r="U61" s="32"/>
-      <c r="V61" s="32"/>
-      <c r="W61" s="32"/>
-      <c r="X61" s="32"/>
-      <c r="Y61" s="32"/>
-    </row>
-    <row r="62" spans="1:25" ht="10.15" customHeight="1">
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="25"/>
+    <row r="54" spans="4:25" s="3" customFormat="1">
+      <c r="D54" s="23"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="4"/>
+      <c r="R54" s="4"/>
+      <c r="S54" s="4"/>
+      <c r="T54" s="4"/>
+      <c r="U54" s="4"/>
+      <c r="V54" s="4"/>
+      <c r="W54" s="4"/>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+    </row>
+    <row r="55" spans="4:25" s="3" customFormat="1">
+      <c r="D55" s="23"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4"/>
+      <c r="T55" s="4"/>
+      <c r="U55" s="4"/>
+      <c r="V55" s="4"/>
+      <c r="W55" s="4"/>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+    </row>
+    <row r="56" spans="4:25" s="3" customFormat="1">
+      <c r="D56" s="23"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="4"/>
+      <c r="S56" s="4"/>
+      <c r="T56" s="4"/>
+      <c r="U56" s="4"/>
+      <c r="V56" s="4"/>
+      <c r="W56" s="4"/>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+    </row>
+    <row r="57" spans="4:25" s="3" customFormat="1">
+      <c r="D57" s="23"/>
+      <c r="E57" s="46"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4"/>
+      <c r="T57" s="4"/>
+      <c r="U57" s="4"/>
+      <c r="V57" s="4"/>
+      <c r="W57" s="4"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+    </row>
+    <row r="58" spans="4:25" s="3" customFormat="1">
+      <c r="D58" s="23"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4"/>
+      <c r="T58" s="4"/>
+      <c r="U58" s="4"/>
+      <c r="V58" s="4"/>
+      <c r="W58" s="4"/>
+      <c r="X58" s="4"/>
+      <c r="Y58" s="4"/>
+    </row>
+    <row r="59" spans="4:25" s="3" customFormat="1">
+      <c r="D59" s="23"/>
+      <c r="E59" s="46"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="4"/>
+      <c r="S59" s="4"/>
+      <c r="T59" s="4"/>
+      <c r="U59" s="4"/>
+      <c r="V59" s="4"/>
+      <c r="W59" s="4"/>
+      <c r="X59" s="4"/>
+      <c r="Y59" s="4"/>
+    </row>
+    <row r="60" spans="4:25" s="3" customFormat="1">
+      <c r="D60" s="23"/>
+      <c r="E60" s="46"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="4"/>
+      <c r="S60" s="4"/>
+      <c r="T60" s="4"/>
+      <c r="U60" s="4"/>
+      <c r="V60" s="4"/>
+      <c r="W60" s="4"/>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+    </row>
+    <row r="61" spans="4:25" s="3" customFormat="1">
+      <c r="D61" s="23"/>
+      <c r="E61" s="46"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4"/>
+      <c r="S61" s="4"/>
+      <c r="T61" s="4"/>
+      <c r="U61" s="4"/>
+      <c r="V61" s="4"/>
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+    </row>
+    <row r="62" spans="4:25" s="3" customFormat="1">
+      <c r="D62" s="23"/>
       <c r="E62" s="46"/>
-    </row>
-    <row r="63" spans="1:25" ht="1.1499999999999999" customHeight="1">
-      <c r="B63" s="19"/>
-      <c r="C63" s="19"/>
-      <c r="D63" s="26"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="4"/>
+      <c r="S62" s="4"/>
+      <c r="T62" s="4"/>
+      <c r="U62" s="4"/>
+      <c r="V62" s="4"/>
+      <c r="W62" s="4"/>
+      <c r="X62" s="4"/>
+      <c r="Y62" s="4"/>
+    </row>
+    <row r="63" spans="4:25" s="3" customFormat="1">
+      <c r="D63" s="23"/>
       <c r="E63" s="46"/>
-    </row>
-    <row r="64" spans="1:25" ht="1.1499999999999999" customHeight="1" thickBot="1">
-      <c r="B64" s="19"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="26"/>
-    </row>
-    <row r="65" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B65" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="C65" s="54"/>
-      <c r="D65" s="71"/>
-      <c r="E65" s="63"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="4"/>
-      <c r="L65" s="4"/>
-      <c r="M65" s="4"/>
-      <c r="N65" s="4"/>
-      <c r="O65" s="4"/>
-      <c r="P65" s="4"/>
-      <c r="Q65" s="4"/>
-      <c r="R65" s="4"/>
-      <c r="S65" s="4"/>
-      <c r="T65" s="4"/>
-      <c r="U65" s="4"/>
-      <c r="V65" s="4"/>
-      <c r="W65" s="4"/>
-      <c r="X65" s="4"/>
-      <c r="Y65" s="4"/>
-    </row>
-    <row r="66" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B66" s="55"/>
-      <c r="C66" s="56"/>
-      <c r="D66" s="72"/>
-      <c r="E66" s="63"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
-      <c r="L66" s="4"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4"/>
-      <c r="O66" s="4"/>
-      <c r="P66" s="4"/>
-      <c r="Q66" s="4"/>
-      <c r="R66" s="4"/>
-      <c r="S66" s="4"/>
-      <c r="T66" s="4"/>
-      <c r="U66" s="4"/>
-      <c r="V66" s="4"/>
-      <c r="W66" s="4"/>
-      <c r="X66" s="4"/>
-      <c r="Y66" s="4"/>
-    </row>
-    <row r="67" spans="1:25" ht="21" customHeight="1">
-      <c r="B67" s="55"/>
-      <c r="C67" s="56"/>
-      <c r="D67" s="72"/>
-      <c r="E67" s="63"/>
-    </row>
-    <row r="68" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
-      <c r="A68" s="31"/>
-      <c r="B68" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="C68" s="65"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="48" t="str">
-        <f>MID(D68,1,6)</f>
-        <v/>
-      </c>
-      <c r="F68" s="32"/>
-      <c r="G68" s="32"/>
-      <c r="H68" s="32"/>
-      <c r="I68" s="32"/>
-      <c r="J68" s="32"/>
-      <c r="K68" s="32"/>
-      <c r="L68" s="32"/>
-      <c r="M68" s="32"/>
-      <c r="N68" s="32"/>
-      <c r="O68" s="32"/>
-      <c r="P68" s="32"/>
-      <c r="Q68" s="32"/>
-      <c r="R68" s="32"/>
-      <c r="S68" s="32"/>
-      <c r="T68" s="32"/>
-      <c r="U68" s="32"/>
-      <c r="V68" s="32"/>
-      <c r="W68" s="32"/>
-      <c r="X68" s="32"/>
-      <c r="Y68" s="32"/>
-    </row>
-    <row r="69" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A69" s="31"/>
-      <c r="B69" s="59" t="str">
-        <f>IF(D68=""," ","Q.ta")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="C69" s="60"/>
-      <c r="D69" s="10"/>
-      <c r="E69" s="48"/>
-      <c r="F69" s="32"/>
-      <c r="G69" s="32"/>
-      <c r="H69" s="32"/>
-      <c r="I69" s="32"/>
-      <c r="J69" s="32"/>
-      <c r="K69" s="32"/>
-      <c r="L69" s="32"/>
-      <c r="M69" s="32"/>
-      <c r="N69" s="32"/>
-      <c r="O69" s="32"/>
-      <c r="P69" s="32"/>
-      <c r="Q69" s="32"/>
-      <c r="R69" s="32"/>
-      <c r="S69" s="32"/>
-      <c r="T69" s="32"/>
-      <c r="U69" s="32"/>
-      <c r="V69" s="32"/>
-      <c r="W69" s="32"/>
-      <c r="X69" s="32"/>
-      <c r="Y69" s="32"/>
-    </row>
-    <row r="70" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A70" s="31"/>
-      <c r="B70" s="59" t="str">
-        <f>IF(E68="INTERN","Caratteristica di lampeggio",IF(E68="FANALI","Caratteristica di lampeggio",""))</f>
-        <v/>
-      </c>
-      <c r="C70" s="60"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="32"/>
-      <c r="I70" s="32"/>
-      <c r="J70" s="32"/>
-      <c r="K70" s="32"/>
-      <c r="L70" s="32"/>
-      <c r="M70" s="32"/>
-      <c r="N70" s="32"/>
-      <c r="O70" s="32"/>
-      <c r="P70" s="32"/>
-      <c r="Q70" s="32"/>
-      <c r="R70" s="32"/>
-      <c r="S70" s="32"/>
-      <c r="T70" s="32"/>
-      <c r="U70" s="32"/>
-      <c r="V70" s="32"/>
-      <c r="W70" s="32"/>
-      <c r="X70" s="32"/>
-      <c r="Y70" s="32"/>
-    </row>
-    <row r="71" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A71" s="31"/>
-      <c r="B71" s="59" t="str">
-        <f>IF(E68="INTERN","Portata                          MN",IF(E68="FANALI","Portata                          MN",""))</f>
-        <v/>
-      </c>
-      <c r="C71" s="60"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="48"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
-      <c r="J71" s="32"/>
-      <c r="K71" s="32"/>
-      <c r="L71" s="32"/>
-      <c r="M71" s="32"/>
-      <c r="N71" s="32"/>
-      <c r="O71" s="32"/>
-      <c r="P71" s="32"/>
-      <c r="Q71" s="32"/>
-      <c r="R71" s="32"/>
-      <c r="S71" s="32"/>
-      <c r="T71" s="32"/>
-      <c r="U71" s="32"/>
-      <c r="V71" s="32"/>
-      <c r="W71" s="32"/>
-      <c r="X71" s="32"/>
-      <c r="Y71" s="32"/>
-    </row>
-    <row r="72" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A72" s="31"/>
-      <c r="B72" s="59" t="str">
-        <f>IF(E68="INTERN","Colore della luce",IF(E68="FANALI","Colore della luce",""))</f>
-        <v/>
-      </c>
-      <c r="C72" s="60"/>
-      <c r="D72" s="15"/>
-      <c r="E72" s="48"/>
-      <c r="F72" s="32"/>
-      <c r="G72" s="32"/>
-      <c r="H72" s="32"/>
-      <c r="I72" s="32"/>
-      <c r="J72" s="32"/>
-      <c r="K72" s="32"/>
-      <c r="L72" s="32"/>
-      <c r="M72" s="32"/>
-      <c r="N72" s="32"/>
-      <c r="O72" s="32"/>
-      <c r="P72" s="32"/>
-      <c r="Q72" s="32"/>
-      <c r="R72" s="32"/>
-      <c r="S72" s="32"/>
-      <c r="T72" s="32"/>
-      <c r="U72" s="32"/>
-      <c r="V72" s="32"/>
-      <c r="W72" s="32"/>
-      <c r="X72" s="32"/>
-      <c r="Y72" s="32"/>
-    </row>
-    <row r="73" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A73" s="31"/>
-      <c r="B73" s="59" t="str">
-        <f>IF(E68="INTERN","Sincronismo GPS",IF(E68="FANALI","Sincronismo GPS",""))</f>
-        <v/>
-      </c>
-      <c r="C73" s="60"/>
-      <c r="D73" s="15"/>
-      <c r="E73" s="48"/>
-      <c r="F73" s="32"/>
-      <c r="G73" s="32"/>
-      <c r="H73" s="32"/>
-      <c r="I73" s="32"/>
-      <c r="J73" s="32"/>
-      <c r="K73" s="32"/>
-      <c r="L73" s="32"/>
-      <c r="M73" s="32"/>
-      <c r="N73" s="32"/>
-      <c r="O73" s="32"/>
-      <c r="P73" s="32"/>
-      <c r="Q73" s="32"/>
-      <c r="R73" s="32"/>
-      <c r="S73" s="32"/>
-      <c r="T73" s="32"/>
-      <c r="U73" s="32"/>
-      <c r="V73" s="32"/>
-      <c r="W73" s="32"/>
-      <c r="X73" s="32"/>
-      <c r="Y73" s="32"/>
-    </row>
-    <row r="74" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="A74" s="31"/>
-      <c r="B74" s="61" t="str">
-        <f>IF(D68=""," ","Note/specifiche")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="C74" s="62"/>
-      <c r="D74" s="51"/>
-      <c r="E74" s="48"/>
-      <c r="F74" s="32"/>
-      <c r="G74" s="32"/>
-      <c r="H74" s="32"/>
-      <c r="I74" s="32"/>
-      <c r="J74" s="32"/>
-      <c r="K74" s="32"/>
-      <c r="L74" s="32"/>
-      <c r="M74" s="32"/>
-      <c r="N74" s="32"/>
-      <c r="O74" s="32"/>
-      <c r="P74" s="32"/>
-      <c r="Q74" s="32"/>
-      <c r="R74" s="32"/>
-      <c r="S74" s="32"/>
-      <c r="T74" s="32"/>
-      <c r="U74" s="32"/>
-      <c r="V74" s="32"/>
-      <c r="W74" s="32"/>
-      <c r="X74" s="32"/>
-      <c r="Y74" s="32"/>
-    </row>
-    <row r="75" spans="1:25" ht="10.15" customHeight="1" thickBot="1">
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="25"/>
-    </row>
-    <row r="76" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B76" s="53" t="s">
-        <v>29</v>
-      </c>
-      <c r="C76" s="54"/>
-      <c r="D76" s="73"/>
-      <c r="E76" s="63"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="4"/>
-      <c r="L76" s="4"/>
-      <c r="M76" s="4"/>
-      <c r="N76" s="4"/>
-      <c r="O76" s="4"/>
-      <c r="P76" s="4"/>
-      <c r="Q76" s="4"/>
-      <c r="R76" s="4"/>
-      <c r="S76" s="4"/>
-      <c r="T76" s="4"/>
-      <c r="U76" s="4"/>
-      <c r="V76" s="4"/>
-      <c r="W76" s="4"/>
-      <c r="X76" s="4"/>
-      <c r="Y76" s="4"/>
-    </row>
-    <row r="77" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B77" s="55"/>
-      <c r="C77" s="56"/>
-      <c r="D77" s="74"/>
-      <c r="E77" s="63"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="4"/>
-      <c r="L77" s="4"/>
-      <c r="M77" s="4"/>
-      <c r="N77" s="4"/>
-      <c r="O77" s="4"/>
-      <c r="P77" s="4"/>
-      <c r="Q77" s="4"/>
-      <c r="R77" s="4"/>
-      <c r="S77" s="4"/>
-      <c r="T77" s="4"/>
-      <c r="U77" s="4"/>
-      <c r="V77" s="4"/>
-      <c r="W77" s="4"/>
-      <c r="X77" s="4"/>
-      <c r="Y77" s="4"/>
-    </row>
-    <row r="78" spans="1:25" ht="21" customHeight="1">
-      <c r="B78" s="55"/>
-      <c r="C78" s="56"/>
-      <c r="D78" s="75"/>
-      <c r="E78" s="63"/>
-    </row>
-    <row r="79" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
-      <c r="A79" s="31"/>
-      <c r="B79" s="64" t="s">
-        <v>0</v>
-      </c>
-      <c r="C79" s="65"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="48" t="str">
-        <f>MID(D79,1,6)</f>
-        <v/>
-      </c>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="32"/>
-      <c r="J79" s="32"/>
-      <c r="K79" s="32"/>
-      <c r="L79" s="32"/>
-      <c r="M79" s="32"/>
-      <c r="N79" s="32"/>
-      <c r="O79" s="32"/>
-      <c r="P79" s="32"/>
-      <c r="Q79" s="32"/>
-      <c r="R79" s="32"/>
-      <c r="S79" s="32"/>
-      <c r="T79" s="32"/>
-      <c r="U79" s="32"/>
-      <c r="V79" s="32"/>
-      <c r="W79" s="32"/>
-      <c r="X79" s="32"/>
-      <c r="Y79" s="32"/>
-    </row>
-    <row r="80" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A80" s="31"/>
-      <c r="B80" s="59" t="str">
-        <f>IF(D79=""," ","Q.ta")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="C80" s="60"/>
-      <c r="D80" s="10"/>
-      <c r="E80" s="48"/>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
-      <c r="H80" s="32"/>
-      <c r="I80" s="32"/>
-      <c r="J80" s="32"/>
-      <c r="K80" s="32"/>
-      <c r="L80" s="32"/>
-      <c r="M80" s="32"/>
-      <c r="N80" s="32"/>
-      <c r="O80" s="32"/>
-      <c r="P80" s="32"/>
-      <c r="Q80" s="32"/>
-      <c r="R80" s="32"/>
-      <c r="S80" s="32"/>
-      <c r="T80" s="32"/>
-      <c r="U80" s="32"/>
-      <c r="V80" s="32"/>
-      <c r="W80" s="32"/>
-      <c r="X80" s="32"/>
-      <c r="Y80" s="32"/>
-    </row>
-    <row r="81" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A81" s="31"/>
-      <c r="B81" s="59" t="str">
-        <f>IF(E79="INTERN","Caratteristica di lampeggio",IF(E79="FANALI","Caratteristica di lampeggio",""))</f>
-        <v/>
-      </c>
-      <c r="C81" s="60"/>
-      <c r="D81" s="13"/>
-      <c r="E81" s="48"/>
-      <c r="F81" s="32"/>
-      <c r="G81" s="32"/>
-      <c r="H81" s="32"/>
-      <c r="I81" s="32"/>
-      <c r="J81" s="32"/>
-      <c r="K81" s="32"/>
-      <c r="L81" s="32"/>
-      <c r="M81" s="32"/>
-      <c r="N81" s="32"/>
-      <c r="O81" s="32"/>
-      <c r="P81" s="32"/>
-      <c r="Q81" s="32"/>
-      <c r="R81" s="32"/>
-      <c r="S81" s="32"/>
-      <c r="T81" s="32"/>
-      <c r="U81" s="32"/>
-      <c r="V81" s="32"/>
-      <c r="W81" s="32"/>
-      <c r="X81" s="32"/>
-      <c r="Y81" s="32"/>
-    </row>
-    <row r="82" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A82" s="31"/>
-      <c r="B82" s="59" t="str">
-        <f>IF(E79="INTERN","Portata                          MN",IF(E79="FANALI","Portata                          MN",""))</f>
-        <v/>
-      </c>
-      <c r="C82" s="60"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="48"/>
-      <c r="F82" s="32"/>
-      <c r="G82" s="32"/>
-      <c r="H82" s="32"/>
-      <c r="I82" s="32"/>
-      <c r="J82" s="32"/>
-      <c r="K82" s="32"/>
-      <c r="L82" s="32"/>
-      <c r="M82" s="32"/>
-      <c r="N82" s="32"/>
-      <c r="O82" s="32"/>
-      <c r="P82" s="32"/>
-      <c r="Q82" s="32"/>
-      <c r="R82" s="32"/>
-      <c r="S82" s="32"/>
-      <c r="T82" s="32"/>
-      <c r="U82" s="32"/>
-      <c r="V82" s="32"/>
-      <c r="W82" s="32"/>
-      <c r="X82" s="32"/>
-      <c r="Y82" s="32"/>
-    </row>
-    <row r="83" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A83" s="31"/>
-      <c r="B83" s="59" t="str">
-        <f>IF(E79="INTERN","Colore della luce",IF(E79="FANALI","Colore della luce",""))</f>
-        <v/>
-      </c>
-      <c r="C83" s="60"/>
-      <c r="D83" s="15"/>
-      <c r="E83" s="48"/>
-      <c r="F83" s="32"/>
-      <c r="G83" s="32"/>
-      <c r="H83" s="32"/>
-      <c r="I83" s="32"/>
-      <c r="J83" s="32"/>
-      <c r="K83" s="32"/>
-      <c r="L83" s="32"/>
-      <c r="M83" s="32"/>
-      <c r="N83" s="32"/>
-      <c r="O83" s="32"/>
-      <c r="P83" s="32"/>
-      <c r="Q83" s="32"/>
-      <c r="R83" s="32"/>
-      <c r="S83" s="32"/>
-      <c r="T83" s="32"/>
-      <c r="U83" s="32"/>
-      <c r="V83" s="32"/>
-      <c r="W83" s="32"/>
-      <c r="X83" s="32"/>
-      <c r="Y83" s="32"/>
-    </row>
-    <row r="84" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A84" s="31"/>
-      <c r="B84" s="59" t="str">
-        <f>IF(E79="INTERN","Sincronismo GPS",IF(E79="FANALI","Sincronismo GPS",""))</f>
-        <v/>
-      </c>
-      <c r="C84" s="60"/>
-      <c r="D84" s="15"/>
-      <c r="E84" s="48"/>
-      <c r="F84" s="32"/>
-      <c r="G84" s="32"/>
-      <c r="H84" s="32"/>
-      <c r="I84" s="32"/>
-      <c r="J84" s="32"/>
-      <c r="K84" s="32"/>
-      <c r="L84" s="32"/>
-      <c r="M84" s="32"/>
-      <c r="N84" s="32"/>
-      <c r="O84" s="32"/>
-      <c r="P84" s="32"/>
-      <c r="Q84" s="32"/>
-      <c r="R84" s="32"/>
-      <c r="S84" s="32"/>
-      <c r="T84" s="32"/>
-      <c r="U84" s="32"/>
-      <c r="V84" s="32"/>
-      <c r="W84" s="32"/>
-      <c r="X84" s="32"/>
-      <c r="Y84" s="32"/>
-    </row>
-    <row r="85" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
-      <c r="A85" s="31"/>
-      <c r="B85" s="61" t="str">
-        <f>IF(D79=""," ","Note/specifiche")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="C85" s="62"/>
-      <c r="D85" s="51"/>
-      <c r="E85" s="48"/>
-      <c r="F85" s="32"/>
-      <c r="G85" s="32"/>
-      <c r="H85" s="32"/>
-      <c r="I85" s="32"/>
-      <c r="J85" s="32"/>
-      <c r="K85" s="32"/>
-      <c r="L85" s="32"/>
-      <c r="M85" s="32"/>
-      <c r="N85" s="32"/>
-      <c r="O85" s="32"/>
-      <c r="P85" s="32"/>
-      <c r="Q85" s="32"/>
-      <c r="R85" s="32"/>
-      <c r="S85" s="32"/>
-      <c r="T85" s="32"/>
-      <c r="U85" s="32"/>
-      <c r="V85" s="32"/>
-      <c r="W85" s="32"/>
-      <c r="X85" s="32"/>
-      <c r="Y85" s="32"/>
-    </row>
-    <row r="86" spans="1:25" s="3" customFormat="1">
-      <c r="D86" s="23"/>
-      <c r="E86" s="46"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="4"/>
-      <c r="H86" s="4"/>
-      <c r="I86" s="4"/>
-      <c r="J86" s="4"/>
-      <c r="K86" s="4"/>
-      <c r="L86" s="4"/>
-      <c r="M86" s="4"/>
-      <c r="N86" s="4"/>
-      <c r="O86" s="4"/>
-      <c r="P86" s="4"/>
-      <c r="Q86" s="4"/>
-      <c r="R86" s="4"/>
-      <c r="S86" s="4"/>
-      <c r="T86" s="4"/>
-      <c r="U86" s="4"/>
-      <c r="V86" s="4"/>
-      <c r="W86" s="4"/>
-      <c r="X86" s="4"/>
-      <c r="Y86" s="4"/>
-    </row>
-    <row r="87" spans="1:25" s="3" customFormat="1">
-      <c r="B87" s="34"/>
-      <c r="D87" s="23"/>
-      <c r="E87" s="46"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="4"/>
-      <c r="H87" s="4"/>
-      <c r="I87" s="4"/>
-      <c r="J87" s="4"/>
-      <c r="K87" s="4"/>
-      <c r="L87" s="4"/>
-      <c r="M87" s="4"/>
-      <c r="N87" s="4"/>
-      <c r="O87" s="4"/>
-      <c r="P87" s="4"/>
-      <c r="Q87" s="4"/>
-      <c r="R87" s="4"/>
-      <c r="S87" s="4"/>
-      <c r="T87" s="4"/>
-      <c r="U87" s="4"/>
-      <c r="V87" s="4"/>
-      <c r="W87" s="4"/>
-      <c r="X87" s="4"/>
-      <c r="Y87" s="4"/>
-    </row>
-    <row r="88" spans="1:25" s="3" customFormat="1">
-      <c r="B88" s="34"/>
-      <c r="D88" s="23"/>
-      <c r="E88" s="46"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
-      <c r="I88" s="4"/>
-      <c r="J88" s="4"/>
-      <c r="K88" s="4"/>
-      <c r="L88" s="4"/>
-      <c r="M88" s="4"/>
-      <c r="N88" s="4"/>
-      <c r="O88" s="4"/>
-      <c r="P88" s="4"/>
-      <c r="Q88" s="4"/>
-      <c r="R88" s="4"/>
-      <c r="S88" s="4"/>
-      <c r="T88" s="4"/>
-      <c r="U88" s="4"/>
-      <c r="V88" s="4"/>
-      <c r="W88" s="4"/>
-      <c r="X88" s="4"/>
-      <c r="Y88" s="4"/>
-    </row>
-    <row r="89" spans="1:25" s="3" customFormat="1">
-      <c r="B89" s="34"/>
-      <c r="D89" s="23"/>
-      <c r="E89" s="46"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
-      <c r="J89" s="4"/>
-      <c r="K89" s="4"/>
-      <c r="L89" s="4"/>
-      <c r="M89" s="4"/>
-      <c r="N89" s="4"/>
-      <c r="O89" s="4"/>
-      <c r="P89" s="4"/>
-      <c r="Q89" s="4"/>
-      <c r="R89" s="4"/>
-      <c r="S89" s="4"/>
-      <c r="T89" s="4"/>
-      <c r="U89" s="4"/>
-      <c r="V89" s="4"/>
-      <c r="W89" s="4"/>
-      <c r="X89" s="4"/>
-      <c r="Y89" s="4"/>
-    </row>
-    <row r="90" spans="1:25" s="3" customFormat="1">
-      <c r="B90" s="34"/>
-      <c r="C90" s="34"/>
-      <c r="D90" s="23"/>
-      <c r="E90" s="46"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
-      <c r="I90" s="4"/>
-      <c r="J90" s="4"/>
-      <c r="K90" s="4"/>
-      <c r="L90" s="4"/>
-      <c r="M90" s="4"/>
-      <c r="N90" s="4"/>
-      <c r="O90" s="4"/>
-      <c r="P90" s="4"/>
-      <c r="Q90" s="4"/>
-      <c r="R90" s="4"/>
-      <c r="S90" s="4"/>
-      <c r="T90" s="4"/>
-      <c r="U90" s="4"/>
-      <c r="V90" s="4"/>
-      <c r="W90" s="4"/>
-      <c r="X90" s="4"/>
-      <c r="Y90" s="4"/>
-    </row>
-    <row r="91" spans="1:25" s="3" customFormat="1">
-      <c r="B91" s="34"/>
-      <c r="C91" s="34"/>
-      <c r="D91" s="23"/>
-      <c r="E91" s="46"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
-      <c r="I91" s="4"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="4"/>
-      <c r="L91" s="4"/>
-      <c r="M91" s="4"/>
-      <c r="N91" s="4"/>
-      <c r="O91" s="4"/>
-      <c r="P91" s="4"/>
-      <c r="Q91" s="4"/>
-      <c r="R91" s="4"/>
-      <c r="S91" s="4"/>
-      <c r="T91" s="4"/>
-      <c r="U91" s="4"/>
-      <c r="V91" s="4"/>
-      <c r="W91" s="4"/>
-      <c r="X91" s="4"/>
-      <c r="Y91" s="4"/>
-    </row>
-    <row r="92" spans="1:25" s="3" customFormat="1">
-      <c r="B92" s="34"/>
-      <c r="C92" s="34"/>
-      <c r="D92" s="23"/>
-      <c r="E92" s="46"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
-      <c r="I92" s="4"/>
-      <c r="J92" s="4"/>
-      <c r="K92" s="4"/>
-      <c r="L92" s="4"/>
-      <c r="M92" s="4"/>
-      <c r="N92" s="4"/>
-      <c r="O92" s="4"/>
-      <c r="P92" s="4"/>
-      <c r="Q92" s="4"/>
-      <c r="R92" s="4"/>
-      <c r="S92" s="4"/>
-      <c r="T92" s="4"/>
-      <c r="U92" s="4"/>
-      <c r="V92" s="4"/>
-      <c r="W92" s="4"/>
-      <c r="X92" s="4"/>
-      <c r="Y92" s="4"/>
-    </row>
-    <row r="93" spans="1:25" s="3" customFormat="1">
-      <c r="B93" s="34"/>
-      <c r="C93" s="34"/>
-      <c r="D93" s="23"/>
-      <c r="E93" s="46"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
-      <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
-      <c r="K93" s="4"/>
-      <c r="L93" s="4"/>
-      <c r="M93" s="4"/>
-      <c r="N93" s="4"/>
-      <c r="O93" s="4"/>
-      <c r="P93" s="4"/>
-      <c r="Q93" s="4"/>
-      <c r="R93" s="4"/>
-      <c r="S93" s="4"/>
-      <c r="T93" s="4"/>
-      <c r="U93" s="4"/>
-      <c r="V93" s="4"/>
-      <c r="W93" s="4"/>
-      <c r="X93" s="4"/>
-      <c r="Y93" s="4"/>
-    </row>
-    <row r="94" spans="1:25" s="3" customFormat="1">
-      <c r="B94" s="34"/>
-      <c r="C94" s="34"/>
-      <c r="D94" s="23"/>
-      <c r="E94" s="46"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
-      <c r="J94" s="4"/>
-      <c r="K94" s="4"/>
-      <c r="L94" s="4"/>
-      <c r="M94" s="4"/>
-      <c r="N94" s="4"/>
-      <c r="O94" s="4"/>
-      <c r="P94" s="4"/>
-      <c r="Q94" s="4"/>
-      <c r="R94" s="4"/>
-      <c r="S94" s="4"/>
-      <c r="T94" s="4"/>
-      <c r="U94" s="4"/>
-      <c r="V94" s="4"/>
-      <c r="W94" s="4"/>
-      <c r="X94" s="4"/>
-      <c r="Y94" s="4"/>
-    </row>
-    <row r="95" spans="1:25" s="3" customFormat="1">
-      <c r="B95" s="34"/>
-      <c r="C95" s="34"/>
-      <c r="D95" s="23"/>
-      <c r="E95" s="46"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
-      <c r="K95" s="4"/>
-      <c r="L95" s="4"/>
-      <c r="M95" s="4"/>
-      <c r="N95" s="4"/>
-      <c r="O95" s="4"/>
-      <c r="P95" s="4"/>
-      <c r="Q95" s="4"/>
-      <c r="R95" s="4"/>
-      <c r="S95" s="4"/>
-      <c r="T95" s="4"/>
-      <c r="U95" s="4"/>
-      <c r="V95" s="4"/>
-      <c r="W95" s="4"/>
-      <c r="X95" s="4"/>
-      <c r="Y95" s="4"/>
-    </row>
-    <row r="96" spans="1:25" s="3" customFormat="1">
-      <c r="B96" s="34"/>
-      <c r="C96" s="34"/>
-      <c r="D96" s="23"/>
-      <c r="E96" s="46"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
-      <c r="I96" s="4"/>
-      <c r="J96" s="4"/>
-      <c r="K96" s="4"/>
-      <c r="L96" s="4"/>
-      <c r="M96" s="4"/>
-      <c r="N96" s="4"/>
-      <c r="O96" s="4"/>
-      <c r="P96" s="4"/>
-      <c r="Q96" s="4"/>
-      <c r="R96" s="4"/>
-      <c r="S96" s="4"/>
-      <c r="T96" s="4"/>
-      <c r="U96" s="4"/>
-      <c r="V96" s="4"/>
-      <c r="W96" s="4"/>
-      <c r="X96" s="4"/>
-      <c r="Y96" s="4"/>
-    </row>
-    <row r="97" spans="4:25" s="3" customFormat="1">
-      <c r="D97" s="23"/>
-      <c r="E97" s="46"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="4"/>
-      <c r="I97" s="4"/>
-      <c r="J97" s="4"/>
-      <c r="K97" s="4"/>
-      <c r="L97" s="4"/>
-      <c r="M97" s="4"/>
-      <c r="N97" s="4"/>
-      <c r="O97" s="4"/>
-      <c r="P97" s="4"/>
-      <c r="Q97" s="4"/>
-      <c r="R97" s="4"/>
-      <c r="S97" s="4"/>
-      <c r="T97" s="4"/>
-      <c r="U97" s="4"/>
-      <c r="V97" s="4"/>
-      <c r="W97" s="4"/>
-      <c r="X97" s="4"/>
-      <c r="Y97" s="4"/>
-    </row>
-    <row r="98" spans="4:25" s="3" customFormat="1">
-      <c r="D98" s="23"/>
-      <c r="E98" s="46"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="4"/>
-      <c r="I98" s="4"/>
-      <c r="J98" s="4"/>
-      <c r="K98" s="4"/>
-      <c r="L98" s="4"/>
-      <c r="M98" s="4"/>
-      <c r="N98" s="4"/>
-      <c r="O98" s="4"/>
-      <c r="P98" s="4"/>
-      <c r="Q98" s="4"/>
-      <c r="R98" s="4"/>
-      <c r="S98" s="4"/>
-      <c r="T98" s="4"/>
-      <c r="U98" s="4"/>
-      <c r="V98" s="4"/>
-      <c r="W98" s="4"/>
-      <c r="X98" s="4"/>
-      <c r="Y98" s="4"/>
-    </row>
-    <row r="99" spans="4:25" s="3" customFormat="1">
-      <c r="D99" s="23"/>
-      <c r="E99" s="46"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
-      <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
-      <c r="K99" s="4"/>
-      <c r="L99" s="4"/>
-      <c r="M99" s="4"/>
-      <c r="N99" s="4"/>
-      <c r="O99" s="4"/>
-      <c r="P99" s="4"/>
-      <c r="Q99" s="4"/>
-      <c r="R99" s="4"/>
-      <c r="S99" s="4"/>
-      <c r="T99" s="4"/>
-      <c r="U99" s="4"/>
-      <c r="V99" s="4"/>
-      <c r="W99" s="4"/>
-      <c r="X99" s="4"/>
-      <c r="Y99" s="4"/>
-    </row>
-    <row r="100" spans="4:25" s="3" customFormat="1">
-      <c r="D100" s="23"/>
-      <c r="E100" s="46"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4"/>
-      <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
-      <c r="K100" s="4"/>
-      <c r="L100" s="4"/>
-      <c r="M100" s="4"/>
-      <c r="N100" s="4"/>
-      <c r="O100" s="4"/>
-      <c r="P100" s="4"/>
-      <c r="Q100" s="4"/>
-      <c r="R100" s="4"/>
-      <c r="S100" s="4"/>
-      <c r="T100" s="4"/>
-      <c r="U100" s="4"/>
-      <c r="V100" s="4"/>
-      <c r="W100" s="4"/>
-      <c r="X100" s="4"/>
-      <c r="Y100" s="4"/>
-    </row>
-    <row r="101" spans="4:25" s="3" customFormat="1">
-      <c r="D101" s="23"/>
-      <c r="E101" s="46"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
-      <c r="H101" s="4"/>
-      <c r="I101" s="4"/>
-      <c r="J101" s="4"/>
-      <c r="K101" s="4"/>
-      <c r="L101" s="4"/>
-      <c r="M101" s="4"/>
-      <c r="N101" s="4"/>
-      <c r="O101" s="4"/>
-      <c r="P101" s="4"/>
-      <c r="Q101" s="4"/>
-      <c r="R101" s="4"/>
-      <c r="S101" s="4"/>
-      <c r="T101" s="4"/>
-      <c r="U101" s="4"/>
-      <c r="V101" s="4"/>
-      <c r="W101" s="4"/>
-      <c r="X101" s="4"/>
-      <c r="Y101" s="4"/>
-    </row>
-    <row r="102" spans="4:25" s="3" customFormat="1">
-      <c r="D102" s="23"/>
-      <c r="E102" s="46"/>
-      <c r="F102" s="4"/>
-      <c r="G102" s="4"/>
-      <c r="H102" s="4"/>
-      <c r="I102" s="4"/>
-      <c r="J102" s="4"/>
-      <c r="K102" s="4"/>
-      <c r="L102" s="4"/>
-      <c r="M102" s="4"/>
-      <c r="N102" s="4"/>
-      <c r="O102" s="4"/>
-      <c r="P102" s="4"/>
-      <c r="Q102" s="4"/>
-      <c r="R102" s="4"/>
-      <c r="S102" s="4"/>
-      <c r="T102" s="4"/>
-      <c r="U102" s="4"/>
-      <c r="V102" s="4"/>
-      <c r="W102" s="4"/>
-      <c r="X102" s="4"/>
-      <c r="Y102" s="4"/>
-    </row>
-    <row r="103" spans="4:25" s="3" customFormat="1">
-      <c r="D103" s="23"/>
-      <c r="E103" s="46"/>
-      <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
-      <c r="H103" s="4"/>
-      <c r="I103" s="4"/>
-      <c r="J103" s="4"/>
-      <c r="K103" s="4"/>
-      <c r="L103" s="4"/>
-      <c r="M103" s="4"/>
-      <c r="N103" s="4"/>
-      <c r="O103" s="4"/>
-      <c r="P103" s="4"/>
-      <c r="Q103" s="4"/>
-      <c r="R103" s="4"/>
-      <c r="S103" s="4"/>
-      <c r="T103" s="4"/>
-      <c r="U103" s="4"/>
-      <c r="V103" s="4"/>
-      <c r="W103" s="4"/>
-      <c r="X103" s="4"/>
-      <c r="Y103" s="4"/>
-    </row>
-    <row r="104" spans="4:25" s="3" customFormat="1">
-      <c r="D104" s="23"/>
-      <c r="E104" s="46"/>
-      <c r="F104" s="4"/>
-      <c r="G104" s="4"/>
-      <c r="H104" s="4"/>
-      <c r="I104" s="4"/>
-      <c r="J104" s="4"/>
-      <c r="K104" s="4"/>
-      <c r="L104" s="4"/>
-      <c r="M104" s="4"/>
-      <c r="N104" s="4"/>
-      <c r="O104" s="4"/>
-      <c r="P104" s="4"/>
-      <c r="Q104" s="4"/>
-      <c r="R104" s="4"/>
-      <c r="S104" s="4"/>
-      <c r="T104" s="4"/>
-      <c r="U104" s="4"/>
-      <c r="V104" s="4"/>
-      <c r="W104" s="4"/>
-      <c r="X104" s="4"/>
-      <c r="Y104" s="4"/>
-    </row>
-    <row r="105" spans="4:25" s="3" customFormat="1">
-      <c r="D105" s="23"/>
-      <c r="E105" s="46"/>
-      <c r="F105" s="4"/>
-      <c r="G105" s="4"/>
-      <c r="H105" s="4"/>
-      <c r="I105" s="4"/>
-      <c r="J105" s="4"/>
-      <c r="K105" s="4"/>
-      <c r="L105" s="4"/>
-      <c r="M105" s="4"/>
-      <c r="N105" s="4"/>
-      <c r="O105" s="4"/>
-      <c r="P105" s="4"/>
-      <c r="Q105" s="4"/>
-      <c r="R105" s="4"/>
-      <c r="S105" s="4"/>
-      <c r="T105" s="4"/>
-      <c r="U105" s="4"/>
-      <c r="V105" s="4"/>
-      <c r="W105" s="4"/>
-      <c r="X105" s="4"/>
-      <c r="Y105" s="4"/>
-    </row>
-    <row r="106" spans="4:25" s="3" customFormat="1">
-      <c r="D106" s="23"/>
-      <c r="E106" s="46"/>
-      <c r="F106" s="4"/>
-      <c r="G106" s="4"/>
-      <c r="H106" s="4"/>
-      <c r="I106" s="4"/>
-      <c r="J106" s="4"/>
-      <c r="K106" s="4"/>
-      <c r="L106" s="4"/>
-      <c r="M106" s="4"/>
-      <c r="N106" s="4"/>
-      <c r="O106" s="4"/>
-      <c r="P106" s="4"/>
-      <c r="Q106" s="4"/>
-      <c r="R106" s="4"/>
-      <c r="S106" s="4"/>
-      <c r="T106" s="4"/>
-      <c r="U106" s="4"/>
-      <c r="V106" s="4"/>
-      <c r="W106" s="4"/>
-      <c r="X106" s="4"/>
-      <c r="Y106" s="4"/>
-    </row>
-    <row r="107" spans="4:25" s="3" customFormat="1">
-      <c r="D107" s="23"/>
-      <c r="E107" s="46"/>
-      <c r="F107" s="4"/>
-      <c r="G107" s="4"/>
-      <c r="H107" s="4"/>
-      <c r="I107" s="4"/>
-      <c r="J107" s="4"/>
-      <c r="K107" s="4"/>
-      <c r="L107" s="4"/>
-      <c r="M107" s="4"/>
-      <c r="N107" s="4"/>
-      <c r="O107" s="4"/>
-      <c r="P107" s="4"/>
-      <c r="Q107" s="4"/>
-      <c r="R107" s="4"/>
-      <c r="S107" s="4"/>
-      <c r="T107" s="4"/>
-      <c r="U107" s="4"/>
-      <c r="V107" s="4"/>
-      <c r="W107" s="4"/>
-      <c r="X107" s="4"/>
-      <c r="Y107" s="4"/>
-    </row>
-    <row r="108" spans="4:25" s="3" customFormat="1">
-      <c r="D108" s="23"/>
-      <c r="E108" s="46"/>
-      <c r="F108" s="4"/>
-      <c r="G108" s="4"/>
-      <c r="H108" s="4"/>
-      <c r="I108" s="4"/>
-      <c r="J108" s="4"/>
-      <c r="K108" s="4"/>
-      <c r="L108" s="4"/>
-      <c r="M108" s="4"/>
-      <c r="N108" s="4"/>
-      <c r="O108" s="4"/>
-      <c r="P108" s="4"/>
-      <c r="Q108" s="4"/>
-      <c r="R108" s="4"/>
-      <c r="S108" s="4"/>
-      <c r="T108" s="4"/>
-      <c r="U108" s="4"/>
-      <c r="V108" s="4"/>
-      <c r="W108" s="4"/>
-      <c r="X108" s="4"/>
-      <c r="Y108" s="4"/>
-    </row>
-    <row r="109" spans="4:25" s="3" customFormat="1">
-      <c r="D109" s="23"/>
-      <c r="E109" s="46"/>
-      <c r="F109" s="4"/>
-      <c r="G109" s="4"/>
-      <c r="H109" s="4"/>
-      <c r="I109" s="4"/>
-      <c r="J109" s="4"/>
-      <c r="K109" s="4"/>
-      <c r="L109" s="4"/>
-      <c r="M109" s="4"/>
-      <c r="N109" s="4"/>
-      <c r="O109" s="4"/>
-      <c r="P109" s="4"/>
-      <c r="Q109" s="4"/>
-      <c r="R109" s="4"/>
-      <c r="S109" s="4"/>
-      <c r="T109" s="4"/>
-      <c r="U109" s="4"/>
-      <c r="V109" s="4"/>
-      <c r="W109" s="4"/>
-      <c r="X109" s="4"/>
-      <c r="Y109" s="4"/>
-    </row>
-    <row r="110" spans="4:25" s="3" customFormat="1">
-      <c r="D110" s="23"/>
-      <c r="E110" s="46"/>
-      <c r="F110" s="4"/>
-      <c r="G110" s="4"/>
-      <c r="H110" s="4"/>
-      <c r="I110" s="4"/>
-      <c r="J110" s="4"/>
-      <c r="K110" s="4"/>
-      <c r="L110" s="4"/>
-      <c r="M110" s="4"/>
-      <c r="N110" s="4"/>
-      <c r="O110" s="4"/>
-      <c r="P110" s="4"/>
-      <c r="Q110" s="4"/>
-      <c r="R110" s="4"/>
-      <c r="S110" s="4"/>
-      <c r="T110" s="4"/>
-      <c r="U110" s="4"/>
-      <c r="V110" s="4"/>
-      <c r="W110" s="4"/>
-      <c r="X110" s="4"/>
-      <c r="Y110" s="4"/>
-    </row>
-    <row r="111" spans="4:25" s="3" customFormat="1">
-      <c r="D111" s="23"/>
-      <c r="E111" s="46"/>
-      <c r="F111" s="4"/>
-      <c r="G111" s="4"/>
-      <c r="H111" s="4"/>
-      <c r="I111" s="4"/>
-      <c r="J111" s="4"/>
-      <c r="K111" s="4"/>
-      <c r="L111" s="4"/>
-      <c r="M111" s="4"/>
-      <c r="N111" s="4"/>
-      <c r="O111" s="4"/>
-      <c r="P111" s="4"/>
-      <c r="Q111" s="4"/>
-      <c r="R111" s="4"/>
-      <c r="S111" s="4"/>
-      <c r="T111" s="4"/>
-      <c r="U111" s="4"/>
-      <c r="V111" s="4"/>
-      <c r="W111" s="4"/>
-      <c r="X111" s="4"/>
-      <c r="Y111" s="4"/>
-    </row>
-    <row r="112" spans="4:25">
-      <c r="E112" s="46"/>
-    </row>
-    <row r="113" spans="5:5">
-      <c r="E113" s="46"/>
-    </row>
-    <row r="114" spans="5:5">
-      <c r="E114" s="46"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
+      <c r="R63" s="4"/>
+      <c r="S63" s="4"/>
+      <c r="T63" s="4"/>
+      <c r="U63" s="4"/>
+      <c r="V63" s="4"/>
+      <c r="W63" s="4"/>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+    </row>
+    <row r="64" spans="4:25">
+      <c r="E64" s="46"/>
+    </row>
+    <row r="65" spans="5:5">
+      <c r="E65" s="46"/>
+    </row>
+    <row r="66" spans="5:5">
+      <c r="E66" s="46"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
-  <mergeCells count="66">
+  <mergeCells count="35">
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
@@ -3996,17 +2847,10 @@
     <mergeCell ref="E31:E33"/>
     <mergeCell ref="D31:D33"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B50:C50"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
@@ -4017,36 +2861,12 @@
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
     <mergeCell ref="D20:D22"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="E76:E78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="E65:E67"/>
-    <mergeCell ref="E52:E54"/>
     <mergeCell ref="E20:E22"/>
-    <mergeCell ref="D52:D54"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
     <mergeCell ref="E1:E3"/>
-    <mergeCell ref="D65:D67"/>
-    <mergeCell ref="D76:D78"/>
     <mergeCell ref="B7:C9"/>
     <mergeCell ref="B20:C22"/>
     <mergeCell ref="B31:C33"/>
-    <mergeCell ref="B52:C54"/>
-    <mergeCell ref="B65:C67"/>
-    <mergeCell ref="B76:C78"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="B44:C44"/>
     <mergeCell ref="B39:C39"/>
@@ -4074,7 +2894,1633 @@
           <x14:formula1>
             <xm:f>Foglio1!$H$3:$H$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D7:D9 D20:D22 D31:D33 D52:D54 D65:D67 D76:D78</xm:sqref>
+          <xm:sqref>D7:D9 D20:D22 D31:D33</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51C59B5A-F1BC-4DB7-A5A2-2B37ED95F473}">
+  <dimension ref="A1:Y67"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" style="3"/>
+    <col min="2" max="2" width="29.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="53.1640625" style="28" customWidth="1"/>
+    <col min="5" max="5" width="23.5" style="47" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" style="4" customWidth="1"/>
+    <col min="7" max="25" width="9.33203125" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" s="9" customFormat="1" ht="61.15" customHeight="1">
+      <c r="A1" s="3"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="47"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+    </row>
+    <row r="2" spans="1:25" ht="16.5">
+      <c r="B2" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="39">
+        <f>Modulo!D5</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="30"/>
+      <c r="E2" s="46"/>
+    </row>
+    <row r="3" spans="1:25" ht="27" customHeight="1">
+      <c r="B3" s="75">
+        <f>Modulo!D4</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="75"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="46"/>
+    </row>
+    <row r="4" spans="1:25" ht="27" customHeight="1" thickBot="1">
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="46"/>
+    </row>
+    <row r="5" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
+      <c r="B5" s="58" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="59"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+    </row>
+    <row r="6" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
+      <c r="B6" s="60"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4"/>
+    </row>
+    <row r="7" spans="1:25" ht="21" customHeight="1">
+      <c r="B7" s="60"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="68"/>
+    </row>
+    <row r="8" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
+      <c r="A8" s="31"/>
+      <c r="B8" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="70"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="48" t="str">
+        <f>MID(D8,1,6)</f>
+        <v/>
+      </c>
+      <c r="F8" s="48">
+        <f>IF(D8="",0,1)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="32"/>
+      <c r="T8" s="32"/>
+      <c r="U8" s="32"/>
+      <c r="V8" s="32"/>
+      <c r="W8" s="32"/>
+      <c r="X8" s="32"/>
+      <c r="Y8" s="32"/>
+    </row>
+    <row r="9" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A9" s="31"/>
+      <c r="B9" s="64" t="str">
+        <f>IF(D8=""," ","Q.ta")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C9" s="65"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="32"/>
+      <c r="P9" s="32"/>
+      <c r="Q9" s="32"/>
+      <c r="R9" s="32"/>
+      <c r="S9" s="32"/>
+      <c r="T9" s="32"/>
+      <c r="U9" s="32"/>
+      <c r="V9" s="32"/>
+      <c r="W9" s="32"/>
+      <c r="X9" s="32"/>
+      <c r="Y9" s="32"/>
+    </row>
+    <row r="10" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A10" s="31"/>
+      <c r="B10" s="64" t="str">
+        <f>IF(E8="INTERN","Caratteristica di lampeggio",IF(E8="FANALI","Caratteristica di lampeggio",""))</f>
+        <v/>
+      </c>
+      <c r="C10" s="65"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="32"/>
+      <c r="S10" s="32"/>
+      <c r="T10" s="32"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="32"/>
+      <c r="W10" s="32"/>
+      <c r="X10" s="32"/>
+      <c r="Y10" s="32"/>
+    </row>
+    <row r="11" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A11" s="31"/>
+      <c r="B11" s="64" t="str">
+        <f>IF(E8="INTERN","Portata                          MN",IF(E8="FANALI","Portata                          MN",""))</f>
+        <v/>
+      </c>
+      <c r="C11" s="65"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="32"/>
+      <c r="Q11" s="32"/>
+      <c r="R11" s="32"/>
+      <c r="S11" s="32"/>
+      <c r="T11" s="32"/>
+      <c r="U11" s="32"/>
+      <c r="V11" s="32"/>
+      <c r="W11" s="32"/>
+      <c r="X11" s="32"/>
+      <c r="Y11" s="32"/>
+    </row>
+    <row r="12" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A12" s="31"/>
+      <c r="B12" s="64" t="str">
+        <f>IF(E8="INTERN","Colore della luce",IF(E8="FANALI","Colore della luce",""))</f>
+        <v/>
+      </c>
+      <c r="C12" s="65"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="32"/>
+      <c r="Q12" s="32"/>
+      <c r="R12" s="32"/>
+      <c r="S12" s="32"/>
+      <c r="T12" s="32"/>
+      <c r="U12" s="32"/>
+      <c r="V12" s="32"/>
+      <c r="W12" s="32"/>
+      <c r="X12" s="32"/>
+      <c r="Y12" s="32"/>
+    </row>
+    <row r="13" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A13" s="31"/>
+      <c r="B13" s="64" t="str">
+        <f>IF(E8="INTERN","Sincronismo GPS",IF(E8="FANALI","Sincronismo GPS",""))</f>
+        <v/>
+      </c>
+      <c r="C13" s="65"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="32"/>
+      <c r="T13" s="32"/>
+      <c r="U13" s="32"/>
+      <c r="V13" s="32"/>
+      <c r="W13" s="32"/>
+      <c r="X13" s="32"/>
+      <c r="Y13" s="32"/>
+    </row>
+    <row r="14" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="A14" s="31"/>
+      <c r="B14" s="66" t="str">
+        <f>IF(D8=""," ","NOTE / SPECIFICHE TECNICHE")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C14" s="67"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="32"/>
+      <c r="R14" s="32"/>
+      <c r="S14" s="32"/>
+      <c r="T14" s="32"/>
+      <c r="U14" s="32"/>
+      <c r="V14" s="32"/>
+      <c r="W14" s="32"/>
+      <c r="X14" s="32"/>
+      <c r="Y14" s="32"/>
+    </row>
+    <row r="15" spans="1:25" ht="10.15" customHeight="1">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="46"/>
+    </row>
+    <row r="16" spans="1:25" ht="1.1499999999999999" customHeight="1">
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="46"/>
+    </row>
+    <row r="17" spans="1:25" ht="1.1499999999999999" customHeight="1" thickBot="1">
+      <c r="B17" s="19"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="26"/>
+    </row>
+    <row r="18" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
+      <c r="B18" s="58" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="59"/>
+      <c r="D18" s="53"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4"/>
+    </row>
+    <row r="19" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
+      <c r="B19" s="60"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4"/>
+    </row>
+    <row r="20" spans="1:25" ht="21" customHeight="1">
+      <c r="B20" s="60"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="68"/>
+    </row>
+    <row r="21" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
+      <c r="A21" s="31"/>
+      <c r="B21" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="70"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="48" t="str">
+        <f>MID(D21,1,6)</f>
+        <v/>
+      </c>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="32"/>
+      <c r="X21" s="32"/>
+      <c r="Y21" s="32"/>
+    </row>
+    <row r="22" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A22" s="31"/>
+      <c r="B22" s="64" t="str">
+        <f>IF(D21=""," ","Q.ta")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C22" s="65"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="32"/>
+      <c r="P22" s="32"/>
+      <c r="Q22" s="32"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="32"/>
+      <c r="U22" s="32"/>
+      <c r="V22" s="32"/>
+      <c r="W22" s="32"/>
+      <c r="X22" s="32"/>
+      <c r="Y22" s="32"/>
+    </row>
+    <row r="23" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A23" s="31"/>
+      <c r="B23" s="64" t="str">
+        <f>IF(E21="INTERN","Caratteristica di lampeggio",IF(E21="FANALI","Caratteristica di lampeggio",""))</f>
+        <v/>
+      </c>
+      <c r="C23" s="65"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="32"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="32"/>
+      <c r="Q23" s="32"/>
+      <c r="R23" s="32"/>
+      <c r="S23" s="32"/>
+      <c r="T23" s="32"/>
+      <c r="U23" s="32"/>
+      <c r="V23" s="32"/>
+      <c r="W23" s="32"/>
+      <c r="X23" s="32"/>
+      <c r="Y23" s="32"/>
+    </row>
+    <row r="24" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A24" s="31"/>
+      <c r="B24" s="64" t="str">
+        <f>IF(E21="INTERN","Portata                          MN",IF(E21="FANALI","Portata                          MN",""))</f>
+        <v/>
+      </c>
+      <c r="C24" s="65"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="32"/>
+      <c r="S24" s="32"/>
+      <c r="T24" s="32"/>
+      <c r="U24" s="32"/>
+      <c r="V24" s="32"/>
+      <c r="W24" s="32"/>
+      <c r="X24" s="32"/>
+      <c r="Y24" s="32"/>
+    </row>
+    <row r="25" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A25" s="31"/>
+      <c r="B25" s="64" t="str">
+        <f>IF(E21="INTERN","Colore della luce",IF(E21="FANALI","Colore della luce",""))</f>
+        <v/>
+      </c>
+      <c r="C25" s="65"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="32"/>
+      <c r="P25" s="32"/>
+      <c r="Q25" s="32"/>
+      <c r="R25" s="32"/>
+      <c r="S25" s="32"/>
+      <c r="T25" s="32"/>
+      <c r="U25" s="32"/>
+      <c r="V25" s="32"/>
+      <c r="W25" s="32"/>
+      <c r="X25" s="32"/>
+      <c r="Y25" s="32"/>
+    </row>
+    <row r="26" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A26" s="31"/>
+      <c r="B26" s="64" t="str">
+        <f>IF(E21="INTERN","Sincronismo GPS",IF(E21="FANALI","Sincronismo GPS",""))</f>
+        <v/>
+      </c>
+      <c r="C26" s="65"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="32"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="32"/>
+      <c r="X26" s="32"/>
+      <c r="Y26" s="32"/>
+    </row>
+    <row r="27" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="A27" s="31"/>
+      <c r="B27" s="66" t="str">
+        <f>IF(D21=""," ","NOTE / SPECIFICHE TECNICHE")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C27" s="67"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="32"/>
+      <c r="O27" s="32"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="32"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="32"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="32"/>
+      <c r="X27" s="32"/>
+      <c r="Y27" s="32"/>
+    </row>
+    <row r="28" spans="1:25" ht="10.15" customHeight="1" thickBot="1">
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="25"/>
+    </row>
+    <row r="29" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
+      <c r="B29" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="59"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="4"/>
+      <c r="T29" s="4"/>
+      <c r="U29" s="4"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="4"/>
+      <c r="X29" s="4"/>
+      <c r="Y29" s="4"/>
+    </row>
+    <row r="30" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
+      <c r="B30" s="60"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="68"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="4"/>
+      <c r="T30" s="4"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="4"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4"/>
+    </row>
+    <row r="31" spans="1:25" ht="21" customHeight="1">
+      <c r="B31" s="60"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="68"/>
+    </row>
+    <row r="32" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
+      <c r="A32" s="31"/>
+      <c r="B32" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" s="70"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="48" t="str">
+        <f>MID(D32,1,6)</f>
+        <v/>
+      </c>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="32"/>
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="32"/>
+      <c r="W32" s="32"/>
+      <c r="X32" s="32"/>
+      <c r="Y32" s="32"/>
+    </row>
+    <row r="33" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A33" s="31"/>
+      <c r="B33" s="64" t="str">
+        <f>IF(D32=""," ","Q.ta")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C33" s="65"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="32"/>
+      <c r="P33" s="32"/>
+      <c r="Q33" s="32"/>
+      <c r="R33" s="32"/>
+      <c r="S33" s="32"/>
+      <c r="T33" s="32"/>
+      <c r="U33" s="32"/>
+      <c r="V33" s="32"/>
+      <c r="W33" s="32"/>
+      <c r="X33" s="32"/>
+      <c r="Y33" s="32"/>
+    </row>
+    <row r="34" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A34" s="31"/>
+      <c r="B34" s="64" t="str">
+        <f>IF(E32="INTERN","Caratteristica di lampeggio",IF(E32="FANALI","Caratteristica di lampeggio",""))</f>
+        <v/>
+      </c>
+      <c r="C34" s="65"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
+      <c r="L34" s="32"/>
+      <c r="M34" s="32"/>
+      <c r="N34" s="32"/>
+      <c r="O34" s="32"/>
+      <c r="P34" s="32"/>
+      <c r="Q34" s="32"/>
+      <c r="R34" s="32"/>
+      <c r="S34" s="32"/>
+      <c r="T34" s="32"/>
+      <c r="U34" s="32"/>
+      <c r="V34" s="32"/>
+      <c r="W34" s="32"/>
+      <c r="X34" s="32"/>
+      <c r="Y34" s="32"/>
+    </row>
+    <row r="35" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A35" s="31"/>
+      <c r="B35" s="64" t="str">
+        <f>IF(E32="INTERN","Portata                          MN",IF(E32="FANALI","Portata                          MN",""))</f>
+        <v/>
+      </c>
+      <c r="C35" s="65"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
+      <c r="L35" s="32"/>
+      <c r="M35" s="32"/>
+      <c r="N35" s="32"/>
+      <c r="O35" s="32"/>
+      <c r="P35" s="32"/>
+      <c r="Q35" s="32"/>
+      <c r="R35" s="32"/>
+      <c r="S35" s="32"/>
+      <c r="T35" s="32"/>
+      <c r="U35" s="32"/>
+      <c r="V35" s="32"/>
+      <c r="W35" s="32"/>
+      <c r="X35" s="32"/>
+      <c r="Y35" s="32"/>
+    </row>
+    <row r="36" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A36" s="31"/>
+      <c r="B36" s="64" t="str">
+        <f>IF(E32="INTERN","Colore della luce",IF(E32="FANALI","Colore della luce",""))</f>
+        <v/>
+      </c>
+      <c r="C36" s="65"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="32"/>
+      <c r="P36" s="32"/>
+      <c r="Q36" s="32"/>
+      <c r="R36" s="32"/>
+      <c r="S36" s="32"/>
+      <c r="T36" s="32"/>
+      <c r="U36" s="32"/>
+      <c r="V36" s="32"/>
+      <c r="W36" s="32"/>
+      <c r="X36" s="32"/>
+      <c r="Y36" s="32"/>
+    </row>
+    <row r="37" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A37" s="31"/>
+      <c r="B37" s="64" t="str">
+        <f>IF(E32="INTERN","Sincronismo GPS",IF(E32="FANALI","Sincronismo GPS",""))</f>
+        <v/>
+      </c>
+      <c r="C37" s="65"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="32"/>
+      <c r="R37" s="32"/>
+      <c r="S37" s="32"/>
+      <c r="T37" s="32"/>
+      <c r="U37" s="32"/>
+      <c r="V37" s="32"/>
+      <c r="W37" s="32"/>
+      <c r="X37" s="32"/>
+      <c r="Y37" s="32"/>
+    </row>
+    <row r="38" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
+      <c r="A38" s="31"/>
+      <c r="B38" s="66" t="str">
+        <f>IF(D32=""," ","NOTE / SPECIFICHE TECNICHE")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="C38" s="67"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
+      <c r="L38" s="32"/>
+      <c r="M38" s="32"/>
+      <c r="N38" s="32"/>
+      <c r="O38" s="32"/>
+      <c r="P38" s="32"/>
+      <c r="Q38" s="32"/>
+      <c r="R38" s="32"/>
+      <c r="S38" s="32"/>
+      <c r="T38" s="32"/>
+      <c r="U38" s="32"/>
+      <c r="V38" s="32"/>
+      <c r="W38" s="32"/>
+      <c r="X38" s="32"/>
+      <c r="Y38" s="32"/>
+    </row>
+    <row r="39" spans="1:25" s="3" customFormat="1">
+      <c r="D39" s="23"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="4"/>
+      <c r="S39" s="4"/>
+      <c r="T39" s="4"/>
+      <c r="U39" s="4"/>
+      <c r="V39" s="4"/>
+      <c r="W39" s="4"/>
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4"/>
+    </row>
+    <row r="40" spans="1:25" s="3" customFormat="1">
+      <c r="B40" s="34"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="46"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="4"/>
+      <c r="T40" s="4"/>
+      <c r="U40" s="4"/>
+      <c r="V40" s="4"/>
+      <c r="W40" s="4"/>
+      <c r="X40" s="4"/>
+      <c r="Y40" s="4"/>
+    </row>
+    <row r="41" spans="1:25" s="3" customFormat="1">
+      <c r="B41" s="34"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="4"/>
+      <c r="T41" s="4"/>
+      <c r="U41" s="4"/>
+      <c r="V41" s="4"/>
+      <c r="W41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+    </row>
+    <row r="42" spans="1:25" s="3" customFormat="1">
+      <c r="B42" s="34"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="4"/>
+      <c r="T42" s="4"/>
+      <c r="U42" s="4"/>
+      <c r="V42" s="4"/>
+      <c r="W42" s="4"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+    </row>
+    <row r="43" spans="1:25" s="3" customFormat="1">
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="4"/>
+      <c r="T43" s="4"/>
+      <c r="U43" s="4"/>
+      <c r="V43" s="4"/>
+      <c r="W43" s="4"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
+    </row>
+    <row r="44" spans="1:25" s="3" customFormat="1">
+      <c r="B44" s="34"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="4"/>
+      <c r="R44" s="4"/>
+      <c r="S44" s="4"/>
+      <c r="T44" s="4"/>
+      <c r="U44" s="4"/>
+      <c r="V44" s="4"/>
+      <c r="W44" s="4"/>
+      <c r="X44" s="4"/>
+      <c r="Y44" s="4"/>
+    </row>
+    <row r="45" spans="1:25" s="3" customFormat="1">
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="4"/>
+      <c r="Q45" s="4"/>
+      <c r="R45" s="4"/>
+      <c r="S45" s="4"/>
+      <c r="T45" s="4"/>
+      <c r="U45" s="4"/>
+      <c r="V45" s="4"/>
+      <c r="W45" s="4"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+    </row>
+    <row r="46" spans="1:25" s="3" customFormat="1">
+      <c r="B46" s="34"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="46"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="4"/>
+      <c r="R46" s="4"/>
+      <c r="S46" s="4"/>
+      <c r="T46" s="4"/>
+      <c r="U46" s="4"/>
+      <c r="V46" s="4"/>
+      <c r="W46" s="4"/>
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4"/>
+    </row>
+    <row r="47" spans="1:25" s="3" customFormat="1">
+      <c r="B47" s="34"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="46"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="4"/>
+      <c r="R47" s="4"/>
+      <c r="S47" s="4"/>
+      <c r="T47" s="4"/>
+      <c r="U47" s="4"/>
+      <c r="V47" s="4"/>
+      <c r="W47" s="4"/>
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4"/>
+    </row>
+    <row r="48" spans="1:25" s="3" customFormat="1">
+      <c r="B48" s="34"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="4"/>
+      <c r="S48" s="4"/>
+      <c r="T48" s="4"/>
+      <c r="U48" s="4"/>
+      <c r="V48" s="4"/>
+      <c r="W48" s="4"/>
+      <c r="X48" s="4"/>
+      <c r="Y48" s="4"/>
+    </row>
+    <row r="49" spans="2:25" s="3" customFormat="1">
+      <c r="B49" s="34"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4"/>
+      <c r="S49" s="4"/>
+      <c r="T49" s="4"/>
+      <c r="U49" s="4"/>
+      <c r="V49" s="4"/>
+      <c r="W49" s="4"/>
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4"/>
+    </row>
+    <row r="50" spans="2:25" s="3" customFormat="1">
+      <c r="D50" s="23"/>
+      <c r="E50" s="46"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="4"/>
+      <c r="S50" s="4"/>
+      <c r="T50" s="4"/>
+      <c r="U50" s="4"/>
+      <c r="V50" s="4"/>
+      <c r="W50" s="4"/>
+      <c r="X50" s="4"/>
+      <c r="Y50" s="4"/>
+    </row>
+    <row r="51" spans="2:25" s="3" customFormat="1">
+      <c r="D51" s="23"/>
+      <c r="E51" s="46"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4"/>
+      <c r="R51" s="4"/>
+      <c r="S51" s="4"/>
+      <c r="T51" s="4"/>
+      <c r="U51" s="4"/>
+      <c r="V51" s="4"/>
+      <c r="W51" s="4"/>
+      <c r="X51" s="4"/>
+      <c r="Y51" s="4"/>
+    </row>
+    <row r="52" spans="2:25" s="3" customFormat="1">
+      <c r="D52" s="23"/>
+      <c r="E52" s="46"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="4"/>
+      <c r="S52" s="4"/>
+      <c r="T52" s="4"/>
+      <c r="U52" s="4"/>
+      <c r="V52" s="4"/>
+      <c r="W52" s="4"/>
+      <c r="X52" s="4"/>
+      <c r="Y52" s="4"/>
+    </row>
+    <row r="53" spans="2:25" s="3" customFormat="1">
+      <c r="D53" s="23"/>
+      <c r="E53" s="46"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4"/>
+      <c r="S53" s="4"/>
+      <c r="T53" s="4"/>
+      <c r="U53" s="4"/>
+      <c r="V53" s="4"/>
+      <c r="W53" s="4"/>
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+    </row>
+    <row r="54" spans="2:25" s="3" customFormat="1">
+      <c r="D54" s="23"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="4"/>
+      <c r="R54" s="4"/>
+      <c r="S54" s="4"/>
+      <c r="T54" s="4"/>
+      <c r="U54" s="4"/>
+      <c r="V54" s="4"/>
+      <c r="W54" s="4"/>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+    </row>
+    <row r="55" spans="2:25" s="3" customFormat="1">
+      <c r="D55" s="23"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4"/>
+      <c r="T55" s="4"/>
+      <c r="U55" s="4"/>
+      <c r="V55" s="4"/>
+      <c r="W55" s="4"/>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+    </row>
+    <row r="56" spans="2:25" s="3" customFormat="1">
+      <c r="D56" s="23"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="4"/>
+      <c r="S56" s="4"/>
+      <c r="T56" s="4"/>
+      <c r="U56" s="4"/>
+      <c r="V56" s="4"/>
+      <c r="W56" s="4"/>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+    </row>
+    <row r="57" spans="2:25" s="3" customFormat="1">
+      <c r="D57" s="23"/>
+      <c r="E57" s="46"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4"/>
+      <c r="T57" s="4"/>
+      <c r="U57" s="4"/>
+      <c r="V57" s="4"/>
+      <c r="W57" s="4"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+    </row>
+    <row r="58" spans="2:25" s="3" customFormat="1">
+      <c r="D58" s="23"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4"/>
+      <c r="T58" s="4"/>
+      <c r="U58" s="4"/>
+      <c r="V58" s="4"/>
+      <c r="W58" s="4"/>
+      <c r="X58" s="4"/>
+      <c r="Y58" s="4"/>
+    </row>
+    <row r="59" spans="2:25" s="3" customFormat="1">
+      <c r="D59" s="23"/>
+      <c r="E59" s="46"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="4"/>
+      <c r="S59" s="4"/>
+      <c r="T59" s="4"/>
+      <c r="U59" s="4"/>
+      <c r="V59" s="4"/>
+      <c r="W59" s="4"/>
+      <c r="X59" s="4"/>
+      <c r="Y59" s="4"/>
+    </row>
+    <row r="60" spans="2:25" s="3" customFormat="1">
+      <c r="D60" s="23"/>
+      <c r="E60" s="46"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="4"/>
+      <c r="S60" s="4"/>
+      <c r="T60" s="4"/>
+      <c r="U60" s="4"/>
+      <c r="V60" s="4"/>
+      <c r="W60" s="4"/>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+    </row>
+    <row r="61" spans="2:25" s="3" customFormat="1">
+      <c r="D61" s="23"/>
+      <c r="E61" s="46"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4"/>
+      <c r="S61" s="4"/>
+      <c r="T61" s="4"/>
+      <c r="U61" s="4"/>
+      <c r="V61" s="4"/>
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+    </row>
+    <row r="62" spans="2:25" s="3" customFormat="1">
+      <c r="D62" s="23"/>
+      <c r="E62" s="46"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="4"/>
+      <c r="S62" s="4"/>
+      <c r="T62" s="4"/>
+      <c r="U62" s="4"/>
+      <c r="V62" s="4"/>
+      <c r="W62" s="4"/>
+      <c r="X62" s="4"/>
+      <c r="Y62" s="4"/>
+    </row>
+    <row r="63" spans="2:25" s="3" customFormat="1">
+      <c r="D63" s="23"/>
+      <c r="E63" s="46"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
+      <c r="R63" s="4"/>
+      <c r="S63" s="4"/>
+      <c r="T63" s="4"/>
+      <c r="U63" s="4"/>
+      <c r="V63" s="4"/>
+      <c r="W63" s="4"/>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+    </row>
+    <row r="64" spans="2:25" s="3" customFormat="1">
+      <c r="D64" s="23"/>
+      <c r="E64" s="46"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4"/>
+      <c r="R64" s="4"/>
+      <c r="S64" s="4"/>
+      <c r="T64" s="4"/>
+      <c r="U64" s="4"/>
+      <c r="V64" s="4"/>
+      <c r="W64" s="4"/>
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4"/>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="E65" s="46"/>
+    </row>
+    <row r="66" spans="1:5" s="4" customFormat="1">
+      <c r="A66" s="3"/>
+      <c r="B66"/>
+      <c r="C66"/>
+      <c r="D66" s="28"/>
+      <c r="E66" s="46"/>
+    </row>
+    <row r="67" spans="1:5" s="4" customFormat="1">
+      <c r="A67" s="3"/>
+      <c r="B67"/>
+      <c r="C67"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="46"/>
+    </row>
+  </sheetData>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
+  <mergeCells count="31">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B29:C31"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="B5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B3:C3"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;RDATA EMISSIONE  &amp;D</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{03044E4A-91C2-4FB9-B5F6-6AE51863B052}">
+          <x14:formula1>
+            <xm:f>Foglio1!$H$3:$H$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>D5:D7 D18:D20 D29:D31</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/modello.xlsx
+++ b/modello.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maurizio\Desktop\progetto_modulo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D984CB9A-173E-4EF5-A687-ECA6A8A6F764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC77A0D9-254B-4D76-B5FD-461ED338D34F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -822,8 +822,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -833,6 +845,45 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -844,57 +895,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -921,15 +921,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>82522</xdr:colOff>
+      <xdr:colOff>101571</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437254</xdr:colOff>
+      <xdr:colOff>638039</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>400050</xdr:rowOff>
+      <xdr:rowOff>476249</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -952,8 +952,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="587347" y="0"/>
-          <a:ext cx="2059707" cy="723900"/>
+          <a:off x="606396" y="95250"/>
+          <a:ext cx="2241443" cy="704849"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1452,7 +1452,7 @@
   <sheetData>
     <row r="1" spans="1:25" s="3" customFormat="1">
       <c r="D1" s="23"/>
-      <c r="E1" s="52"/>
+      <c r="E1" s="65"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
@@ -1478,7 +1478,7 @@
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="24"/>
-      <c r="E2" s="52"/>
+      <c r="E2" s="65"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -1500,25 +1500,25 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
     </row>
-    <row r="3" spans="1:25" ht="34.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:25" ht="41.25" customHeight="1" thickBot="1">
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="24"/>
-      <c r="E3" s="52"/>
+      <c r="E3" s="65"/>
     </row>
     <row r="4" spans="1:25" ht="27" customHeight="1">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="72"/>
+      <c r="C4" s="60"/>
       <c r="D4" s="36"/>
       <c r="E4" s="46"/>
     </row>
     <row r="5" spans="1:25" ht="27" customHeight="1" thickBot="1">
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="74"/>
+      <c r="C5" s="62"/>
       <c r="D5" s="35"/>
       <c r="E5" s="46"/>
     </row>
@@ -1528,12 +1528,12 @@
       <c r="D6" s="12"/>
     </row>
     <row r="7" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="59"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="68"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="56"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -1556,10 +1556,10 @@
       <c r="Y7" s="4"/>
     </row>
     <row r="8" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B8" s="60"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="68"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="56"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -1582,17 +1582,17 @@
       <c r="Y8" s="4"/>
     </row>
     <row r="9" spans="1:25" ht="21" customHeight="1">
-      <c r="B9" s="60"/>
-      <c r="C9" s="61"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="68"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="56"/>
     </row>
     <row r="10" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
       <c r="A10" s="31"/>
-      <c r="B10" s="69" t="s">
+      <c r="B10" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="70"/>
+      <c r="C10" s="64"/>
       <c r="D10" s="43"/>
       <c r="E10" s="48" t="str">
         <f>MID(D10,1,6)</f>
@@ -1621,11 +1621,11 @@
     </row>
     <row r="11" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A11" s="31"/>
-      <c r="B11" s="64" t="str">
+      <c r="B11" s="52" t="str">
         <f>IF(D10=""," ","Q.ta")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C11" s="65"/>
+      <c r="C11" s="53"/>
       <c r="D11" s="40"/>
       <c r="E11" s="48"/>
       <c r="F11" s="32"/>
@@ -1651,11 +1651,11 @@
     </row>
     <row r="12" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A12" s="31"/>
-      <c r="B12" s="64" t="str">
+      <c r="B12" s="52" t="str">
         <f>IF(E10="INTERN","Caratteristica di lampeggio",IF(E10="FANALI","Caratteristica di lampeggio",""))</f>
         <v/>
       </c>
-      <c r="C12" s="65"/>
+      <c r="C12" s="53"/>
       <c r="D12" s="41"/>
       <c r="E12" s="48"/>
       <c r="F12" s="32"/>
@@ -1681,11 +1681,11 @@
     </row>
     <row r="13" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A13" s="31"/>
-      <c r="B13" s="64" t="str">
+      <c r="B13" s="52" t="str">
         <f>IF(E10="INTERN","Portata                          MN",IF(E10="FANALI","Portata                          MN",""))</f>
         <v/>
       </c>
-      <c r="C13" s="65"/>
+      <c r="C13" s="53"/>
       <c r="D13" s="42"/>
       <c r="E13" s="48"/>
       <c r="F13" s="32"/>
@@ -1711,11 +1711,11 @@
     </row>
     <row r="14" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A14" s="31"/>
-      <c r="B14" s="64" t="str">
+      <c r="B14" s="52" t="str">
         <f>IF(E10="INTERN","Colore della luce",IF(E10="FANALI","Colore della luce",""))</f>
         <v/>
       </c>
-      <c r="C14" s="65"/>
+      <c r="C14" s="53"/>
       <c r="D14" s="42"/>
       <c r="E14" s="48" t="s">
         <v>41</v>
@@ -1743,11 +1743,11 @@
     </row>
     <row r="15" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A15" s="31"/>
-      <c r="B15" s="64" t="str">
+      <c r="B15" s="52" t="str">
         <f>IF(E10="INTERN","Sincronismo GPS",IF(E10="FANALI","Sincronismo GPS",""))</f>
         <v/>
       </c>
-      <c r="C15" s="65"/>
+      <c r="C15" s="53"/>
       <c r="D15" s="42"/>
       <c r="E15" s="48"/>
       <c r="F15" s="32"/>
@@ -1773,11 +1773,11 @@
     </row>
     <row r="16" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A16" s="31"/>
-      <c r="B16" s="66" t="str">
+      <c r="B16" s="54" t="str">
         <f>IF(D10=""," ","NOTE / SPECIFICHE TECNICHE")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C16" s="67"/>
+      <c r="C16" s="55"/>
       <c r="D16" s="44"/>
       <c r="E16" s="48"/>
       <c r="F16" s="32"/>
@@ -1819,12 +1819,12 @@
       <c r="D19" s="26"/>
     </row>
     <row r="20" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="59"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="68"/>
+      <c r="C20" s="67"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="56"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
@@ -1847,10 +1847,10 @@
       <c r="Y20" s="4"/>
     </row>
     <row r="21" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B21" s="60"/>
-      <c r="C21" s="61"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="68"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="56"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
@@ -1873,17 +1873,17 @@
       <c r="Y21" s="4"/>
     </row>
     <row r="22" spans="1:25" ht="21" customHeight="1">
-      <c r="B22" s="60"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="54"/>
-      <c r="E22" s="68"/>
+      <c r="B22" s="68"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="56"/>
     </row>
     <row r="23" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
       <c r="A23" s="31"/>
-      <c r="B23" s="69" t="s">
+      <c r="B23" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C23" s="70"/>
+      <c r="C23" s="64"/>
       <c r="D23" s="43"/>
       <c r="E23" s="48" t="str">
         <f>MID(D23,1,6)</f>
@@ -1912,11 +1912,11 @@
     </row>
     <row r="24" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A24" s="31"/>
-      <c r="B24" s="64" t="str">
+      <c r="B24" s="52" t="str">
         <f>IF(D23=""," ","Q.ta")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C24" s="65"/>
+      <c r="C24" s="53"/>
       <c r="D24" s="40"/>
       <c r="E24" s="48"/>
       <c r="F24" s="32"/>
@@ -1942,11 +1942,11 @@
     </row>
     <row r="25" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A25" s="31"/>
-      <c r="B25" s="64" t="str">
+      <c r="B25" s="52" t="str">
         <f>IF(E23="INTERN","Caratteristica di lampeggio",IF(E23="FANALI","Caratteristica di lampeggio",""))</f>
         <v/>
       </c>
-      <c r="C25" s="65"/>
+      <c r="C25" s="53"/>
       <c r="D25" s="41"/>
       <c r="E25" s="48"/>
       <c r="F25" s="32"/>
@@ -1972,11 +1972,11 @@
     </row>
     <row r="26" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A26" s="31"/>
-      <c r="B26" s="64" t="str">
+      <c r="B26" s="52" t="str">
         <f>IF(E23="INTERN","Portata                          MN",IF(E23="FANALI","Portata                          MN",""))</f>
         <v/>
       </c>
-      <c r="C26" s="65"/>
+      <c r="C26" s="53"/>
       <c r="D26" s="42"/>
       <c r="E26" s="48"/>
       <c r="F26" s="32"/>
@@ -2002,11 +2002,11 @@
     </row>
     <row r="27" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A27" s="31"/>
-      <c r="B27" s="64" t="str">
+      <c r="B27" s="52" t="str">
         <f>IF(E23="INTERN","Colore della luce",IF(E23="FANALI","Colore della luce",""))</f>
         <v/>
       </c>
-      <c r="C27" s="65"/>
+      <c r="C27" s="53"/>
       <c r="D27" s="42"/>
       <c r="E27" s="48"/>
       <c r="F27" s="32"/>
@@ -2032,11 +2032,11 @@
     </row>
     <row r="28" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A28" s="31"/>
-      <c r="B28" s="64" t="str">
+      <c r="B28" s="52" t="str">
         <f>IF(E23="INTERN","Sincronismo GPS",IF(E23="FANALI","Sincronismo GPS",""))</f>
         <v/>
       </c>
-      <c r="C28" s="65"/>
+      <c r="C28" s="53"/>
       <c r="D28" s="42"/>
       <c r="E28" s="48"/>
       <c r="F28" s="32"/>
@@ -2062,11 +2062,11 @@
     </row>
     <row r="29" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A29" s="31"/>
-      <c r="B29" s="66" t="str">
+      <c r="B29" s="54" t="str">
         <f>IF(D23=""," ","NOTE / SPECIFICHE TECNICHE")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C29" s="67"/>
+      <c r="C29" s="55"/>
       <c r="D29" s="44"/>
       <c r="E29" s="48"/>
       <c r="F29" s="32"/>
@@ -2096,12 +2096,12 @@
       <c r="D30" s="25"/>
     </row>
     <row r="31" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B31" s="58" t="s">
+      <c r="B31" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="59"/>
-      <c r="D31" s="53"/>
-      <c r="E31" s="68"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="56"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -2124,10 +2124,10 @@
       <c r="Y31" s="4"/>
     </row>
     <row r="32" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B32" s="60"/>
-      <c r="C32" s="61"/>
-      <c r="D32" s="54"/>
-      <c r="E32" s="68"/>
+      <c r="B32" s="68"/>
+      <c r="C32" s="69"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="56"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
@@ -2150,17 +2150,17 @@
       <c r="Y32" s="4"/>
     </row>
     <row r="33" spans="1:25" ht="21" customHeight="1">
-      <c r="B33" s="60"/>
-      <c r="C33" s="61"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="68"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="58"/>
+      <c r="E33" s="56"/>
     </row>
     <row r="34" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
       <c r="A34" s="31"/>
-      <c r="B34" s="69" t="s">
+      <c r="B34" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C34" s="70"/>
+      <c r="C34" s="64"/>
       <c r="D34" s="43"/>
       <c r="E34" s="48" t="str">
         <f>MID(D34,1,6)</f>
@@ -2189,11 +2189,11 @@
     </row>
     <row r="35" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A35" s="31"/>
-      <c r="B35" s="64" t="str">
+      <c r="B35" s="52" t="str">
         <f>IF(D34=""," ","Q.ta")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C35" s="65"/>
+      <c r="C35" s="53"/>
       <c r="D35" s="40"/>
       <c r="E35" s="48"/>
       <c r="F35" s="32"/>
@@ -2219,11 +2219,11 @@
     </row>
     <row r="36" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A36" s="31"/>
-      <c r="B36" s="64" t="str">
+      <c r="B36" s="52" t="str">
         <f>IF(E34="INTERN","Caratteristica di lampeggio",IF(E34="FANALI","Caratteristica di lampeggio",""))</f>
         <v/>
       </c>
-      <c r="C36" s="65"/>
+      <c r="C36" s="53"/>
       <c r="D36" s="41"/>
       <c r="E36" s="48"/>
       <c r="F36" s="32"/>
@@ -2249,11 +2249,11 @@
     </row>
     <row r="37" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A37" s="31"/>
-      <c r="B37" s="64" t="str">
+      <c r="B37" s="52" t="str">
         <f>IF(E34="INTERN","Portata                          MN",IF(E34="FANALI","Portata                          MN",""))</f>
         <v/>
       </c>
-      <c r="C37" s="65"/>
+      <c r="C37" s="53"/>
       <c r="D37" s="42"/>
       <c r="E37" s="48"/>
       <c r="F37" s="32"/>
@@ -2279,11 +2279,11 @@
     </row>
     <row r="38" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A38" s="31"/>
-      <c r="B38" s="64" t="str">
+      <c r="B38" s="52" t="str">
         <f>IF(E34="INTERN","Colore della luce",IF(E34="FANALI","Colore della luce",""))</f>
         <v/>
       </c>
-      <c r="C38" s="65"/>
+      <c r="C38" s="53"/>
       <c r="D38" s="42"/>
       <c r="E38" s="48"/>
       <c r="F38" s="32"/>
@@ -2309,11 +2309,11 @@
     </row>
     <row r="39" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A39" s="31"/>
-      <c r="B39" s="64" t="str">
+      <c r="B39" s="52" t="str">
         <f>IF(E34="INTERN","Sincronismo GPS",IF(E34="FANALI","Sincronismo GPS",""))</f>
         <v/>
       </c>
-      <c r="C39" s="65"/>
+      <c r="C39" s="53"/>
       <c r="D39" s="42"/>
       <c r="E39" s="48"/>
       <c r="F39" s="32"/>
@@ -2339,11 +2339,11 @@
     </row>
     <row r="40" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A40" s="31"/>
-      <c r="B40" s="66" t="str">
+      <c r="B40" s="54" t="str">
         <f>IF(D34=""," ","NOTE / SPECIFICHE TECNICHE")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C40" s="67"/>
+      <c r="C40" s="55"/>
       <c r="D40" s="44"/>
       <c r="E40" s="48"/>
       <c r="F40" s="32"/>
@@ -2374,10 +2374,10 @@
       <c r="E41" s="46"/>
     </row>
     <row r="42" spans="1:25" ht="15" thickBot="1">
-      <c r="B42" s="62" t="s">
+      <c r="B42" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="63"/>
+      <c r="C42" s="71"/>
       <c r="D42" s="16"/>
       <c r="E42" s="46"/>
     </row>
@@ -2387,10 +2387,10 @@
       <c r="E43" s="46"/>
     </row>
     <row r="44" spans="1:25" ht="13.5" thickBot="1">
-      <c r="B44" s="62" t="s">
+      <c r="B44" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="C44" s="63"/>
+      <c r="C44" s="71"/>
       <c r="D44" s="17"/>
       <c r="E44" s="46"/>
     </row>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="E45" s="46"/>
     </row>
-    <row r="46" spans="1:25" ht="21.6" customHeight="1">
+    <row r="46" spans="1:25" ht="18" customHeight="1">
       <c r="B46" s="20" t="s">
         <v>30</v>
       </c>
@@ -2839,18 +2839,17 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="35">
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="B7:C9"/>
+    <mergeCell ref="B20:C22"/>
+    <mergeCell ref="B31:C33"/>
+    <mergeCell ref="B42:C42"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
@@ -2861,19 +2860,20 @@
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B36:C36"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="D20:D22"/>
     <mergeCell ref="E20:E22"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="B7:C9"/>
-    <mergeCell ref="B20:C22"/>
-    <mergeCell ref="B31:C33"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
@@ -2911,8 +2911,8 @@
     <col min="2" max="2" width="29.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" customWidth="1"/>
     <col min="4" max="4" width="53.1640625" style="28" customWidth="1"/>
-    <col min="5" max="5" width="23.5" style="47" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="23.5" style="47" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" style="4" hidden="1" customWidth="1"/>
     <col min="7" max="25" width="9.33203125" style="4"/>
   </cols>
   <sheetData>
@@ -2972,12 +2972,12 @@
       <c r="E4" s="46"/>
     </row>
     <row r="5" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="59"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="68"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="56"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -3000,10 +3000,10 @@
       <c r="Y5" s="4"/>
     </row>
     <row r="6" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B6" s="60"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="68"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="56"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -3026,17 +3026,17 @@
       <c r="Y6" s="4"/>
     </row>
     <row r="7" spans="1:25" ht="21" customHeight="1">
-      <c r="B7" s="60"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="68"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="56"/>
     </row>
     <row r="8" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
       <c r="A8" s="31"/>
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="70"/>
+      <c r="C8" s="64"/>
       <c r="D8" s="11"/>
       <c r="E8" s="48" t="str">
         <f>MID(D8,1,6)</f>
@@ -3068,11 +3068,11 @@
     </row>
     <row r="9" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A9" s="31"/>
-      <c r="B9" s="64" t="str">
+      <c r="B9" s="52" t="str">
         <f>IF(D8=""," ","Q.ta")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C9" s="65"/>
+      <c r="C9" s="53"/>
       <c r="D9" s="10"/>
       <c r="E9" s="48"/>
       <c r="F9" s="32"/>
@@ -3098,11 +3098,11 @@
     </row>
     <row r="10" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A10" s="31"/>
-      <c r="B10" s="64" t="str">
+      <c r="B10" s="52" t="str">
         <f>IF(E8="INTERN","Caratteristica di lampeggio",IF(E8="FANALI","Caratteristica di lampeggio",""))</f>
         <v/>
       </c>
-      <c r="C10" s="65"/>
+      <c r="C10" s="53"/>
       <c r="D10" s="13"/>
       <c r="E10" s="48"/>
       <c r="F10" s="32"/>
@@ -3128,11 +3128,11 @@
     </row>
     <row r="11" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A11" s="31"/>
-      <c r="B11" s="64" t="str">
+      <c r="B11" s="52" t="str">
         <f>IF(E8="INTERN","Portata                          MN",IF(E8="FANALI","Portata                          MN",""))</f>
         <v/>
       </c>
-      <c r="C11" s="65"/>
+      <c r="C11" s="53"/>
       <c r="D11" s="14"/>
       <c r="E11" s="48"/>
       <c r="F11" s="32"/>
@@ -3158,11 +3158,11 @@
     </row>
     <row r="12" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A12" s="31"/>
-      <c r="B12" s="64" t="str">
+      <c r="B12" s="52" t="str">
         <f>IF(E8="INTERN","Colore della luce",IF(E8="FANALI","Colore della luce",""))</f>
         <v/>
       </c>
-      <c r="C12" s="65"/>
+      <c r="C12" s="53"/>
       <c r="D12" s="15"/>
       <c r="E12" s="48" t="s">
         <v>41</v>
@@ -3190,11 +3190,11 @@
     </row>
     <row r="13" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A13" s="31"/>
-      <c r="B13" s="64" t="str">
+      <c r="B13" s="52" t="str">
         <f>IF(E8="INTERN","Sincronismo GPS",IF(E8="FANALI","Sincronismo GPS",""))</f>
         <v/>
       </c>
-      <c r="C13" s="65"/>
+      <c r="C13" s="53"/>
       <c r="D13" s="15"/>
       <c r="E13" s="48"/>
       <c r="F13" s="32"/>
@@ -3220,11 +3220,11 @@
     </row>
     <row r="14" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A14" s="31"/>
-      <c r="B14" s="66" t="str">
+      <c r="B14" s="54" t="str">
         <f>IF(D8=""," ","NOTE / SPECIFICHE TECNICHE")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C14" s="67"/>
+      <c r="C14" s="55"/>
       <c r="D14" s="51"/>
       <c r="E14" s="48"/>
       <c r="F14" s="32"/>
@@ -3266,12 +3266,12 @@
       <c r="D17" s="26"/>
     </row>
     <row r="18" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="59"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="68"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="56"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -3294,10 +3294,10 @@
       <c r="Y18" s="4"/>
     </row>
     <row r="19" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B19" s="60"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="68"/>
+      <c r="B19" s="68"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="56"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -3320,17 +3320,17 @@
       <c r="Y19" s="4"/>
     </row>
     <row r="20" spans="1:25" ht="21" customHeight="1">
-      <c r="B20" s="60"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="68"/>
+      <c r="B20" s="68"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="56"/>
     </row>
     <row r="21" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
       <c r="A21" s="31"/>
-      <c r="B21" s="69" t="s">
+      <c r="B21" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="70"/>
+      <c r="C21" s="64"/>
       <c r="D21" s="11"/>
       <c r="E21" s="48" t="str">
         <f>MID(D21,1,6)</f>
@@ -3359,11 +3359,11 @@
     </row>
     <row r="22" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A22" s="31"/>
-      <c r="B22" s="64" t="str">
+      <c r="B22" s="52" t="str">
         <f>IF(D21=""," ","Q.ta")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C22" s="65"/>
+      <c r="C22" s="53"/>
       <c r="D22" s="10"/>
       <c r="E22" s="48"/>
       <c r="F22" s="32"/>
@@ -3389,11 +3389,11 @@
     </row>
     <row r="23" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A23" s="31"/>
-      <c r="B23" s="64" t="str">
+      <c r="B23" s="52" t="str">
         <f>IF(E21="INTERN","Caratteristica di lampeggio",IF(E21="FANALI","Caratteristica di lampeggio",""))</f>
         <v/>
       </c>
-      <c r="C23" s="65"/>
+      <c r="C23" s="53"/>
       <c r="D23" s="13"/>
       <c r="E23" s="48"/>
       <c r="F23" s="32"/>
@@ -3419,11 +3419,11 @@
     </row>
     <row r="24" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A24" s="31"/>
-      <c r="B24" s="64" t="str">
+      <c r="B24" s="52" t="str">
         <f>IF(E21="INTERN","Portata                          MN",IF(E21="FANALI","Portata                          MN",""))</f>
         <v/>
       </c>
-      <c r="C24" s="65"/>
+      <c r="C24" s="53"/>
       <c r="D24" s="14"/>
       <c r="E24" s="48"/>
       <c r="F24" s="32"/>
@@ -3449,11 +3449,11 @@
     </row>
     <row r="25" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A25" s="31"/>
-      <c r="B25" s="64" t="str">
+      <c r="B25" s="52" t="str">
         <f>IF(E21="INTERN","Colore della luce",IF(E21="FANALI","Colore della luce",""))</f>
         <v/>
       </c>
-      <c r="C25" s="65"/>
+      <c r="C25" s="53"/>
       <c r="D25" s="15"/>
       <c r="E25" s="48"/>
       <c r="F25" s="32"/>
@@ -3479,11 +3479,11 @@
     </row>
     <row r="26" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A26" s="31"/>
-      <c r="B26" s="64" t="str">
+      <c r="B26" s="52" t="str">
         <f>IF(E21="INTERN","Sincronismo GPS",IF(E21="FANALI","Sincronismo GPS",""))</f>
         <v/>
       </c>
-      <c r="C26" s="65"/>
+      <c r="C26" s="53"/>
       <c r="D26" s="15"/>
       <c r="E26" s="48"/>
       <c r="F26" s="32"/>
@@ -3509,11 +3509,11 @@
     </row>
     <row r="27" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A27" s="31"/>
-      <c r="B27" s="66" t="str">
+      <c r="B27" s="54" t="str">
         <f>IF(D21=""," ","NOTE / SPECIFICHE TECNICHE")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C27" s="67"/>
+      <c r="C27" s="55"/>
       <c r="D27" s="51"/>
       <c r="E27" s="48"/>
       <c r="F27" s="32"/>
@@ -3543,12 +3543,12 @@
       <c r="D28" s="25"/>
     </row>
     <row r="29" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B29" s="58" t="s">
+      <c r="B29" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="59"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="68"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="72"/>
+      <c r="E29" s="56"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
@@ -3571,10 +3571,10 @@
       <c r="Y29" s="4"/>
     </row>
     <row r="30" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B30" s="60"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="68"/>
+      <c r="B30" s="68"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="56"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
@@ -3597,17 +3597,17 @@
       <c r="Y30" s="4"/>
     </row>
     <row r="31" spans="1:25" ht="21" customHeight="1">
-      <c r="B31" s="60"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="68"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="69"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="56"/>
     </row>
     <row r="32" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
       <c r="A32" s="31"/>
-      <c r="B32" s="69" t="s">
+      <c r="B32" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C32" s="70"/>
+      <c r="C32" s="64"/>
       <c r="D32" s="11"/>
       <c r="E32" s="48" t="str">
         <f>MID(D32,1,6)</f>
@@ -3636,11 +3636,11 @@
     </row>
     <row r="33" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A33" s="31"/>
-      <c r="B33" s="64" t="str">
+      <c r="B33" s="52" t="str">
         <f>IF(D32=""," ","Q.ta")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C33" s="65"/>
+      <c r="C33" s="53"/>
       <c r="D33" s="10"/>
       <c r="E33" s="48"/>
       <c r="F33" s="32"/>
@@ -3666,11 +3666,11 @@
     </row>
     <row r="34" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A34" s="31"/>
-      <c r="B34" s="64" t="str">
+      <c r="B34" s="52" t="str">
         <f>IF(E32="INTERN","Caratteristica di lampeggio",IF(E32="FANALI","Caratteristica di lampeggio",""))</f>
         <v/>
       </c>
-      <c r="C34" s="65"/>
+      <c r="C34" s="53"/>
       <c r="D34" s="13"/>
       <c r="E34" s="48"/>
       <c r="F34" s="32"/>
@@ -3696,11 +3696,11 @@
     </row>
     <row r="35" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A35" s="31"/>
-      <c r="B35" s="64" t="str">
+      <c r="B35" s="52" t="str">
         <f>IF(E32="INTERN","Portata                          MN",IF(E32="FANALI","Portata                          MN",""))</f>
         <v/>
       </c>
-      <c r="C35" s="65"/>
+      <c r="C35" s="53"/>
       <c r="D35" s="14"/>
       <c r="E35" s="48"/>
       <c r="F35" s="32"/>
@@ -3726,11 +3726,11 @@
     </row>
     <row r="36" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A36" s="31"/>
-      <c r="B36" s="64" t="str">
+      <c r="B36" s="52" t="str">
         <f>IF(E32="INTERN","Colore della luce",IF(E32="FANALI","Colore della luce",""))</f>
         <v/>
       </c>
-      <c r="C36" s="65"/>
+      <c r="C36" s="53"/>
       <c r="D36" s="15"/>
       <c r="E36" s="48"/>
       <c r="F36" s="32"/>
@@ -3756,11 +3756,11 @@
     </row>
     <row r="37" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A37" s="31"/>
-      <c r="B37" s="64" t="str">
+      <c r="B37" s="52" t="str">
         <f>IF(E32="INTERN","Sincronismo GPS",IF(E32="FANALI","Sincronismo GPS",""))</f>
         <v/>
       </c>
-      <c r="C37" s="65"/>
+      <c r="C37" s="53"/>
       <c r="D37" s="15"/>
       <c r="E37" s="48"/>
       <c r="F37" s="32"/>
@@ -3786,11 +3786,11 @@
     </row>
     <row r="38" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A38" s="31"/>
-      <c r="B38" s="66" t="str">
+      <c r="B38" s="54" t="str">
         <f>IF(D32=""," ","NOTE / SPECIFICHE TECNICHE")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C38" s="67"/>
+      <c r="C38" s="55"/>
       <c r="D38" s="51"/>
       <c r="E38" s="48"/>
       <c r="F38" s="32"/>
@@ -4475,16 +4475,18 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="31">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B29:C31"/>
-    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B18:C20"/>
     <mergeCell ref="E29:E31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="E18:E20"/>
@@ -4493,19 +4495,17 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B18:C20"/>
     <mergeCell ref="D18:D20"/>
-    <mergeCell ref="B5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B29:C31"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>

--- a/modello.xlsx
+++ b/modello.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maurizio\Desktop\progetto_modulo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC77A0D9-254B-4D76-B5FD-461ED338D34F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93534E47-83E2-48EA-9FB4-3D70E4A79CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="6" state="hidden" r:id="rId1"/>
-    <sheet name="Modulo" sheetId="7" r:id="rId2"/>
-    <sheet name="Pagina 2 ( allegato)" sheetId="8" r:id="rId3"/>
+    <sheet name="Pagina1" sheetId="7" r:id="rId2"/>
+    <sheet name="Allegato" sheetId="8" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Modulo!$B$1:$D$47</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Pagina 2 ( allegato)'!$B$1:$D$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">Allegato!$B$1:$D$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Pagina1!$B$1:$D$47</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -171,7 +171,7 @@
     <t xml:space="preserve">allegato 1          </t>
   </si>
   <si>
-    <t>Segue allegato</t>
+    <t>Vedi  allegato</t>
   </si>
 </sst>
 </file>
@@ -181,7 +181,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mmmm/yyyy"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -307,6 +307,13 @@
       <name val="Arial MT"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -637,7 +644,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -814,27 +821,33 @@
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -845,17 +858,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -863,26 +867,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -896,8 +885,29 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1446,13 +1456,14 @@
     <col min="3" max="3" width="12.6640625" customWidth="1"/>
     <col min="4" max="4" width="53.1640625" style="28" customWidth="1"/>
     <col min="5" max="5" width="23.5" style="47" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="9.33203125" style="4" customWidth="1"/>
-    <col min="7" max="25" width="8.83203125" style="4"/>
+    <col min="6" max="6" width="9.33203125" style="4" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="0" style="4" hidden="1" customWidth="1"/>
+    <col min="8" max="25" width="8.83203125" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" s="3" customFormat="1">
       <c r="D1" s="23"/>
-      <c r="E1" s="65"/>
+      <c r="E1" s="71"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
@@ -1478,7 +1489,7 @@
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="24"/>
-      <c r="E2" s="65"/>
+      <c r="E2" s="71"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -1504,21 +1515,21 @@
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
       <c r="D3" s="24"/>
-      <c r="E3" s="65"/>
+      <c r="E3" s="71"/>
     </row>
     <row r="4" spans="1:25" ht="27" customHeight="1">
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="60"/>
+      <c r="C4" s="73"/>
       <c r="D4" s="36"/>
       <c r="E4" s="46"/>
     </row>
     <row r="5" spans="1:25" ht="27" customHeight="1" thickBot="1">
-      <c r="B5" s="61" t="s">
+      <c r="B5" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="62"/>
+      <c r="C5" s="75"/>
       <c r="D5" s="35"/>
       <c r="E5" s="46"/>
     </row>
@@ -1528,12 +1539,12 @@
       <c r="D6" s="12"/>
     </row>
     <row r="7" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="67"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="56"/>
+      <c r="C7" s="56"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="61"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -1556,10 +1567,10 @@
       <c r="Y7" s="4"/>
     </row>
     <row r="8" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B8" s="68"/>
-      <c r="C8" s="69"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="56"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="61"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -1582,17 +1593,17 @@
       <c r="Y8" s="4"/>
     </row>
     <row r="9" spans="1:25" ht="21" customHeight="1">
-      <c r="B9" s="68"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="56"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="60"/>
+      <c r="E9" s="61"/>
     </row>
     <row r="10" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
       <c r="A10" s="31"/>
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="64"/>
+      <c r="C10" s="63"/>
       <c r="D10" s="43"/>
       <c r="E10" s="48" t="str">
         <f>MID(D10,1,6)</f>
@@ -1773,11 +1784,11 @@
     </row>
     <row r="16" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A16" s="31"/>
-      <c r="B16" s="54" t="str">
+      <c r="B16" s="64" t="str">
         <f>IF(D10=""," ","NOTE / SPECIFICHE TECNICHE")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C16" s="55"/>
+      <c r="C16" s="65"/>
       <c r="D16" s="44"/>
       <c r="E16" s="48"/>
       <c r="F16" s="32"/>
@@ -1819,12 +1830,12 @@
       <c r="D19" s="26"/>
     </row>
     <row r="20" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B20" s="66" t="s">
+      <c r="B20" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="67"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="61"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
@@ -1847,10 +1858,10 @@
       <c r="Y20" s="4"/>
     </row>
     <row r="21" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B21" s="68"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="56"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="61"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
@@ -1873,17 +1884,17 @@
       <c r="Y21" s="4"/>
     </row>
     <row r="22" spans="1:25" ht="21" customHeight="1">
-      <c r="B22" s="68"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="56"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="61"/>
     </row>
     <row r="23" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
       <c r="A23" s="31"/>
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="C23" s="64"/>
+      <c r="C23" s="63"/>
       <c r="D23" s="43"/>
       <c r="E23" s="48" t="str">
         <f>MID(D23,1,6)</f>
@@ -2062,11 +2073,11 @@
     </row>
     <row r="29" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A29" s="31"/>
-      <c r="B29" s="54" t="str">
+      <c r="B29" s="64" t="str">
         <f>IF(D23=""," ","NOTE / SPECIFICHE TECNICHE")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C29" s="55"/>
+      <c r="C29" s="65"/>
       <c r="D29" s="44"/>
       <c r="E29" s="48"/>
       <c r="F29" s="32"/>
@@ -2096,12 +2107,12 @@
       <c r="D30" s="25"/>
     </row>
     <row r="31" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B31" s="66" t="s">
+      <c r="B31" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="C31" s="67"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="56"/>
+      <c r="C31" s="56"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="61"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
@@ -2124,10 +2135,10 @@
       <c r="Y31" s="4"/>
     </row>
     <row r="32" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B32" s="68"/>
-      <c r="C32" s="69"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="56"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="61"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
@@ -2150,17 +2161,17 @@
       <c r="Y32" s="4"/>
     </row>
     <row r="33" spans="1:25" ht="21" customHeight="1">
-      <c r="B33" s="68"/>
-      <c r="C33" s="69"/>
-      <c r="D33" s="58"/>
-      <c r="E33" s="56"/>
+      <c r="B33" s="57"/>
+      <c r="C33" s="58"/>
+      <c r="D33" s="60"/>
+      <c r="E33" s="61"/>
     </row>
     <row r="34" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
       <c r="A34" s="31"/>
-      <c r="B34" s="63" t="s">
+      <c r="B34" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="C34" s="64"/>
+      <c r="C34" s="63"/>
       <c r="D34" s="43"/>
       <c r="E34" s="48" t="str">
         <f>MID(D34,1,6)</f>
@@ -2339,11 +2350,11 @@
     </row>
     <row r="40" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A40" s="31"/>
-      <c r="B40" s="54" t="str">
+      <c r="B40" s="64" t="str">
         <f>IF(D34=""," ","NOTE / SPECIFICHE TECNICHE")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C40" s="55"/>
+      <c r="C40" s="65"/>
       <c r="D40" s="44"/>
       <c r="E40" s="48"/>
       <c r="F40" s="32"/>
@@ -2374,10 +2385,10 @@
       <c r="E41" s="46"/>
     </row>
     <row r="42" spans="1:25" ht="15" thickBot="1">
-      <c r="B42" s="70" t="s">
+      <c r="B42" s="69" t="s">
         <v>36</v>
       </c>
-      <c r="C42" s="71"/>
+      <c r="C42" s="70"/>
       <c r="D42" s="16"/>
       <c r="E42" s="46"/>
     </row>
@@ -2387,10 +2398,10 @@
       <c r="E43" s="46"/>
     </row>
     <row r="44" spans="1:25" ht="13.5" thickBot="1">
-      <c r="B44" s="70" t="s">
+      <c r="B44" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="C44" s="71"/>
+      <c r="C44" s="70"/>
       <c r="D44" s="17"/>
       <c r="E44" s="46"/>
     </row>
@@ -2406,8 +2417,8 @@
         <v>30</v>
       </c>
       <c r="C46" s="20"/>
-      <c r="D46" s="50" t="str">
-        <f>IFERROR(IF('Pagina 2 ( allegato)'!F8=1,E46,""),"")</f>
+      <c r="D46" s="51" t="str">
+        <f>IFERROR(IF(Allegato!F8=1,E46,""),"")</f>
         <v/>
       </c>
       <c r="E46" s="46" t="s">
@@ -2441,10 +2452,13 @@
       <c r="X47" s="4"/>
       <c r="Y47" s="4"/>
     </row>
-    <row r="48" spans="1:25" s="3" customFormat="1">
-      <c r="B48" s="34"/>
-      <c r="C48" s="34"/>
-      <c r="D48" s="23"/>
+    <row r="48" spans="1:25" s="3" customFormat="1" ht="30.75" customHeight="1">
+      <c r="B48" s="76" t="str">
+        <f>IFERROR(IF(Allegato!F8=1,"RICORDATI DI STAMPARE ANCHE IL FOGLIO ALLEGATO",""),"")</f>
+        <v/>
+      </c>
+      <c r="C48" s="76"/>
+      <c r="D48" s="76"/>
       <c r="E48" s="46"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -2467,7 +2481,7 @@
       <c r="X48" s="4"/>
       <c r="Y48" s="4"/>
     </row>
-    <row r="49" spans="4:25" s="3" customFormat="1">
+    <row r="49" spans="4:25" s="3" customFormat="1" ht="25.5" customHeight="1">
       <c r="D49" s="23"/>
       <c r="E49" s="46"/>
       <c r="F49" s="4"/>
@@ -2838,13 +2852,16 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
-  <mergeCells count="35">
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="D7:D9"/>
+  <mergeCells count="36">
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E1:E3"/>
     <mergeCell ref="B7:C9"/>
     <mergeCell ref="B20:C22"/>
@@ -2861,17 +2878,15 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="E31:E33"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="D7:D9"/>
     <mergeCell ref="D31:D33"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D20:D22"/>
     <mergeCell ref="E20:E22"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B29:C29"/>
   </mergeCells>
@@ -2894,7 +2909,7 @@
           <x14:formula1>
             <xm:f>Foglio1!$H$3:$H$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D7:D9 D20:D22 D31:D33</xm:sqref>
+          <xm:sqref>D7:D9</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2950,18 +2965,18 @@
         <v>42</v>
       </c>
       <c r="C2" s="39">
-        <f>Modulo!D5</f>
+        <f>Pagina1!D5</f>
         <v>0</v>
       </c>
       <c r="D2" s="30"/>
       <c r="E2" s="46"/>
     </row>
     <row r="3" spans="1:25" ht="27" customHeight="1">
-      <c r="B3" s="75">
-        <f>Modulo!D4</f>
+      <c r="B3" s="54">
+        <f>Pagina1!D4</f>
         <v>0</v>
       </c>
-      <c r="C3" s="75"/>
+      <c r="C3" s="54"/>
       <c r="D3" s="33"/>
       <c r="E3" s="46"/>
     </row>
@@ -2972,12 +2987,12 @@
       <c r="E4" s="46"/>
     </row>
     <row r="5" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="67"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="61"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -3000,10 +3015,10 @@
       <c r="Y5" s="4"/>
     </row>
     <row r="6" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B6" s="68"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="56"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="61"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -3026,17 +3041,17 @@
       <c r="Y6" s="4"/>
     </row>
     <row r="7" spans="1:25" ht="21" customHeight="1">
-      <c r="B7" s="68"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="56"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="61"/>
     </row>
     <row r="8" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
       <c r="A8" s="31"/>
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="64"/>
+      <c r="C8" s="63"/>
       <c r="D8" s="11"/>
       <c r="E8" s="48" t="str">
         <f>MID(D8,1,6)</f>
@@ -3220,12 +3235,12 @@
     </row>
     <row r="14" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A14" s="31"/>
-      <c r="B14" s="54" t="str">
+      <c r="B14" s="64" t="str">
         <f>IF(D8=""," ","NOTE / SPECIFICHE TECNICHE")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C14" s="55"/>
-      <c r="D14" s="51"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="50"/>
       <c r="E14" s="48"/>
       <c r="F14" s="32"/>
       <c r="G14" s="32"/>
@@ -3266,12 +3281,12 @@
       <c r="D17" s="26"/>
     </row>
     <row r="18" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B18" s="66" t="s">
+      <c r="B18" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="67"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="56"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="61"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
@@ -3294,10 +3309,10 @@
       <c r="Y18" s="4"/>
     </row>
     <row r="19" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B19" s="68"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="56"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="61"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
@@ -3320,17 +3335,17 @@
       <c r="Y19" s="4"/>
     </row>
     <row r="20" spans="1:25" ht="21" customHeight="1">
-      <c r="B20" s="68"/>
-      <c r="C20" s="69"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="56"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="61"/>
     </row>
     <row r="21" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
       <c r="A21" s="31"/>
-      <c r="B21" s="63" t="s">
+      <c r="B21" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="64"/>
+      <c r="C21" s="63"/>
       <c r="D21" s="11"/>
       <c r="E21" s="48" t="str">
         <f>MID(D21,1,6)</f>
@@ -3509,12 +3524,12 @@
     </row>
     <row r="27" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A27" s="31"/>
-      <c r="B27" s="54" t="str">
+      <c r="B27" s="64" t="str">
         <f>IF(D21=""," ","NOTE / SPECIFICHE TECNICHE")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C27" s="55"/>
-      <c r="D27" s="51"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="50"/>
       <c r="E27" s="48"/>
       <c r="F27" s="32"/>
       <c r="G27" s="32"/>
@@ -3543,12 +3558,12 @@
       <c r="D28" s="25"/>
     </row>
     <row r="29" spans="1:25" s="3" customFormat="1" ht="20.45" customHeight="1">
-      <c r="B29" s="66" t="s">
+      <c r="B29" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="67"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="56"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="61"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
@@ -3571,10 +3586,10 @@
       <c r="Y29" s="4"/>
     </row>
     <row r="30" spans="1:25" s="3" customFormat="1" ht="6" customHeight="1">
-      <c r="B30" s="68"/>
-      <c r="C30" s="69"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="56"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="58"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="61"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
@@ -3597,17 +3612,17 @@
       <c r="Y30" s="4"/>
     </row>
     <row r="31" spans="1:25" ht="21" customHeight="1">
-      <c r="B31" s="68"/>
-      <c r="C31" s="69"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="56"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="61"/>
     </row>
     <row r="32" spans="1:25" s="6" customFormat="1" ht="28.15" customHeight="1">
       <c r="A32" s="31"/>
-      <c r="B32" s="63" t="s">
+      <c r="B32" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="C32" s="64"/>
+      <c r="C32" s="63"/>
       <c r="D32" s="11"/>
       <c r="E32" s="48" t="str">
         <f>MID(D32,1,6)</f>
@@ -3786,12 +3801,12 @@
     </row>
     <row r="38" spans="1:25" s="6" customFormat="1" ht="21" customHeight="1" thickBot="1">
       <c r="A38" s="31"/>
-      <c r="B38" s="54" t="str">
+      <c r="B38" s="64" t="str">
         <f>IF(D32=""," ","NOTE / SPECIFICHE TECNICHE")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C38" s="55"/>
-      <c r="D38" s="51"/>
+      <c r="C38" s="65"/>
+      <c r="D38" s="50"/>
       <c r="E38" s="48"/>
       <c r="F38" s="32"/>
       <c r="G38" s="32"/>
@@ -4475,27 +4490,6 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="31">
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B18:C20"/>
-    <mergeCell ref="E29:E31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="E18:E20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D18:D20"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
@@ -4506,6 +4500,27 @@
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B37:C37"/>
+    <mergeCell ref="E29:E31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="E18:E20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D18:D20"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B18:C20"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
@@ -4520,7 +4535,7 @@
           <x14:formula1>
             <xm:f>Foglio1!$H$3:$H$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D5:D7 D18:D20 D29:D31</xm:sqref>
+          <xm:sqref>D5:D7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
